--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
@@ -1355,11 +1355,19 @@
       </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>Tomada por Bryan el 14-09-2026 con el centro de la OT en la web (Ficha/Asignación/Pasos/Indisponibilidad/Cierre). El alta desde la app ya existía. Pendiente validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="69" customHeight="1" s="19">
       <c r="A7" s="13" t="inlineStr">
@@ -1631,11 +1639,19 @@
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P10" s="12" t="inlineStr">
+        <is>
+          <t>Tomada por Bryan el 14-09-2026: pestaña Cierre y cierre masivo; UPD_ORDEN_TRABAJO_CERRAR_WEB. Anular desde cualquier estado sólo por la web: el cierre del teléfono sigue exigiendo espera de cierre.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="69" customHeight="1" s="19">
       <c r="A11" s="13" t="inlineStr">
@@ -1769,13 +1785,17 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O12" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>· ALCANCE APP (30-08): Web → Web y App. Promovida a App: el supervisor reasigna en planta cuando alguien no llega.</t>
+          <t>Tomada por Bryan el 14-09-2026: modal de asignación + POST/GET asignaciones. Un solo responsable y advertencia de especialidad las decide el SP. Pendiente la pantalla Flutter de reasignación (T-5901).</t>
         </is>
       </c>
     </row>
@@ -2049,11 +2069,19 @@
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P16" s="12" t="inlineStr">
+        <is>
+          <t>Tomada por Bryan el 14-09-2026: la bandeja es el mismo listado con estado 3, ordenada por antigüedad y con cierre masivo.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55.2" customHeight="1" s="19">
       <c r="A17" s="13" t="inlineStr">
@@ -2254,11 +2282,19 @@
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="14" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O19" s="14" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P19" s="14" t="inlineStr">
+        <is>
+          <t>Tomada por Bryan el 14-09-2026: centro de la falla (diagnósticos y acciones como hilos) + /fallas en la API. Pendiente pantalla Flutter (T-5175) y validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="69" customHeight="1" s="19">
       <c r="A20" s="11" t="inlineStr">
@@ -2321,11 +2357,19 @@
       </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O20" s="12" t="n"/>
-      <c r="P20" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P20" s="12" t="inlineStr">
+        <is>
+          <t>Tomada por Bryan el 14-09-2026: modal desde la OT y la falla + /activo-indisponibilidades. Pendiente consumo desde la app (T-5190).</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="96.59999999999999" customHeight="1" s="19">
       <c r="A21" s="13" t="inlineStr">
@@ -3266,11 +3310,17 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>Orden_Trabajo revisada: UX cliente+correlativo, CK origen; se agregó otr_falla (origen 7 FALLA) al alta web.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="41.4" customHeight="1" s="19">
       <c r="A7" s="11" t="inlineStr">
@@ -3303,16 +3353,22 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>BD/225 INS_ORDEN_TRABAJO (web): área obligatoria sin equipo, registro posterior con dos fechas, origen MANUAL/FALLA, correlativo con UPDLOCK, historial.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="27.6" customHeight="1" s="19">
       <c r="A8" s="11" t="inlineStr">
@@ -3345,16 +3401,22 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>SEL_ORDEN_TRABAJO: listado, ficha y bandeja (con @ESTADO=3 ordena por antigüedad y calcula DIAS_ESPERA_CIERRE); filtro @FALLA.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="27.6" customHeight="1" s="19">
       <c r="A9" s="11" t="inlineStr">
@@ -3392,11 +3454,17 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>UPD_ORDEN_TRABAJO: sólo mientras no esté cerrada; dónde y registro posterior se fijan al crear.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="27.6" customHeight="1" s="19">
       <c r="A10" s="11" t="inlineStr">
@@ -3429,16 +3497,22 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="n"/>
-      <c r="J10" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>OT-13/14 (SP), OT-15 (web desde falla F-1), OT-16/17 (API desde fallas).</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="27.6" customHeight="1" s="19">
       <c r="A11" s="11" t="inlineStr">
@@ -3476,11 +3550,17 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía POST /ordenes-trabajo (app, API_INS_ORDEN_TRABAJO, uuid). Se agregó POST /fallas/{id}/orden: correctiva de emergencia con origen FALLA.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="27.6" customHeight="1" s="19">
       <c r="A12" s="11" t="inlineStr">
@@ -3513,16 +3593,22 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n"/>
-      <c r="J12" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>Ya existían GET /ordenes-trabajo y /{id}; se agregó GET /{id}/asignaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="27.6" customHeight="1" s="19">
       <c r="A13" s="11" t="inlineStr">
@@ -3560,11 +3646,17 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>DTOs FallaOrdenDto / OrdenTrabajoAsignacionAltaDto; nombres del cuerpo son los del DTO.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="27.6" customHeight="1" s="19">
       <c r="A14" s="11" t="inlineStr">
@@ -3602,11 +3694,17 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>OrdenTrabajo.aspx: centro con pestañas Ficha / Asignación / Pasos / Indisponibilidad / Cierre (Default.master, ids cifrados).</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="27.6" customHeight="1" s="19">
       <c r="A15" s="11" t="inlineStr">
@@ -3639,16 +3737,22 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>OrdenTrabajos.aspx: filtro de estado (abiertas por defecto), tipo y planta; chips de prioridad y estado; pasos resueltos.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -3690,7 +3794,11 @@
         </is>
       </c>
       <c r="I16" s="11" t="n"/>
-      <c r="J16" s="12" t="n"/>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>No aplica en este bloque: el alta desde el teléfono ya existía (HU-110 app).</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55.2" customHeight="1" s="19">
       <c r="A17" s="11" t="inlineStr">
@@ -3728,11 +3836,17 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>Menus + Menu_Funcion «Crear y editar» (CREAR ORDEN TRABAJO) y «Cerrar» (CERRAR OT); SP filtran por @CLIENTE; API ExigirPermiso/ExigirCliente.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="41.4" customHeight="1" s="19">
       <c r="A18" s="11" t="inlineStr">
@@ -3765,16 +3879,22 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="n"/>
-      <c r="J18" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>#1 alta (web y API 201) · #2 técnico no cierra (API 403; SP rechaza por FNC_USUARIO_PUEDE_CERRAR_OT) · #3 registro posterior (SP, fechas distintas) · #4 orden sobre área sin equipo (SP).</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="41.4" customHeight="1" s="19">
       <c r="A19" s="11" t="inlineStr">
@@ -3807,16 +3927,22 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>XML en FallasController/OrdenesTrabajoController; MD 10.10.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="27.6" customHeight="1" s="19">
       <c r="A20" s="11" t="inlineStr">
@@ -3849,16 +3975,22 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="n"/>
-      <c r="J20" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente de la PO; la historia queda En revisión.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="41.4" customHeight="1" s="19">
       <c r="A21" s="11" t="inlineStr">
@@ -5504,11 +5636,17 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="n"/>
-      <c r="J58" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J58" s="12" t="inlineStr">
+        <is>
+          <t>Revisado: otr_cierre_motivo, otr_resultado, otr_fecha_cierre, otr_usuario_cierre.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="55.2" customHeight="1" s="19">
       <c r="A59" s="11" t="inlineStr">
@@ -5541,16 +5679,22 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I59" s="11" t="n"/>
-      <c r="J59" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I59" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J59" s="12" t="inlineStr">
+        <is>
+          <t>BD/225 UPD_ORDEN_TRABAJO_CERRAR_WEB con XACT_ABORT: jerarquía por FNC_USUARIO_PUEDE_CERRAR_OT, motivos 1-3 exigen espera de cierre, anular/duplicada/no aplica desde cualquier estado; completa u omite la ocurrencia del plan.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="41.4" customHeight="1" s="19">
       <c r="A60" s="11" t="inlineStr">
@@ -5583,16 +5727,22 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="n"/>
-      <c r="J60" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J60" s="12" t="inlineStr">
+        <is>
+          <t>La regla vive en el SP; la web sólo esconde el botón por la función «Cerrar». El cierre del teléfono (UPD_ORDEN_TRABAJO_CERRAR) no se tocó.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="41.4" customHeight="1" s="19">
       <c r="A61" s="11" t="inlineStr">
@@ -5630,11 +5780,17 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I61" s="11" t="n"/>
-      <c r="J61" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J61" s="12" t="inlineStr">
+        <is>
+          <t>El resultado del cierre lo devuelve SEL_ORDEN_TRABAJO (motivo, resultado, usuario, fecha).</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="27.6" customHeight="1" s="19">
       <c r="A62" s="11" t="inlineStr">
@@ -5667,16 +5823,22 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="n"/>
-      <c r="J62" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J62" s="12" t="inlineStr">
+        <is>
+          <t>OT-2/3/4 en espera de cierre (semilla); OT-3 y OT-4 cerradas desde la bandeja.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="41.4" customHeight="1" s="19">
       <c r="A63" s="11" t="inlineStr">
@@ -5709,16 +5871,22 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I63" s="11" t="n"/>
-      <c r="J63" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J63" s="12" t="inlineStr">
+        <is>
+          <t>Sin pantalla suelta: pestaña Cierre en OrdenTrabajo.aspx (motivo + trabajo realizado, ConfirSweetAlert) y cierre masivo en OrdenTrabajos.aspx.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="27.6" customHeight="1" s="19">
       <c r="A64" s="11" t="inlineStr">
@@ -5756,11 +5924,17 @@
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="n"/>
-      <c r="J64" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J64" s="12" t="inlineStr">
+        <is>
+          <t>Menu_Funcion «Cerrar» → CERRAR OT (perfiles 12,1,5,11); el SP vuelve a validar con la función.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="27.6" customHeight="1" s="19">
       <c r="A65" s="11" t="inlineStr">
@@ -5793,16 +5967,22 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I65" s="11" t="n"/>
-      <c r="J65" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J65" s="12" t="inlineStr">
+        <is>
+          <t>#1 cierre normal (bandeja, web) · #2 técnico no cierra (SP y API 403) · #3 anular desde ABIERTA (SP OT-13) · #4 resultado obligatorio con «Trabajo realizado» (SP). En navegador: intento de cerrar OT-15 abierta → mensaje 6 del SP.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="27.6" customHeight="1" s="19">
       <c r="A66" s="11" t="inlineStr">
@@ -5835,16 +6015,22 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="n"/>
-      <c r="J66" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J66" s="12" t="inlineStr">
+        <is>
+          <t>MD 10.10.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="27.6" customHeight="1" s="19">
       <c r="A67" s="11" t="inlineStr">
@@ -6302,11 +6488,17 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="n"/>
-      <c r="J77" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J77" s="12" t="inlineStr">
+        <is>
+          <t>Orden_Trabajo_Asignacion: UX_OTA_RESPONSABLE (filtrado, un responsable por OT), CK_OTA_EJECUTANTE (usuario XOR proveedor).</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="27.6" customHeight="1" s="19">
       <c r="A78" s="11" t="inlineStr">
@@ -6339,16 +6531,22 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="n"/>
-      <c r="J78" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J78" s="12" t="inlineStr">
+        <is>
+          <t>BD/225 INS_ORDEN_TRABAJO_ASIGNACION: valida contratista, deja un único responsable (el anterior pasa a apoyo), advierte especialidad faltante, INS_NOTIFICACION si existe.</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="27.6" customHeight="1" s="19">
       <c r="A79" s="11" t="inlineStr">
@@ -6381,16 +6579,22 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I79" s="11" t="n"/>
-      <c r="J79" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J79" s="12" t="inlineStr">
+        <is>
+          <t>Web y API llaman al mismo SP; la advertencia vuelve como result set (OTA_ID, ADVERTENCIA).</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="27.6" customHeight="1" s="19">
       <c r="A80" s="11" t="inlineStr">
@@ -6428,11 +6632,17 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="n"/>
-      <c r="J80" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J80" s="12" t="inlineStr">
+        <is>
+          <t>SEL_ORDEN_TRABAJO_ASIGNACION con nombres, rol, especialidades y quién asignó.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="55.2" customHeight="1" s="19">
       <c r="A81" s="11" t="inlineStr">
@@ -6465,16 +6675,22 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I81" s="11" t="n"/>
-      <c r="J81" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J81" s="12" t="inlineStr">
+        <is>
+          <t>OT-14 (SP) y OT-15/16 (web y API) con cambio de responsable.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="41.4" customHeight="1" s="19">
       <c r="A82" s="11" t="inlineStr">
@@ -6507,16 +6723,22 @@
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="n"/>
-      <c r="J82" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="12" t="inlineStr">
+        <is>
+          <t>POST /ordenes-trabajo/{id}/asignaciones; DELETE /ordenes-trabajo/asignaciones/{id}.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="41.4" customHeight="1" s="19">
       <c r="A83" s="11" t="inlineStr">
@@ -6554,11 +6776,17 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="n"/>
-      <c r="J83" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J83" s="12" t="inlineStr">
+        <is>
+          <t>RAISERROR numerados del SP → 400 con mensaje (ApiBase.Ejecutar); "usuario y proveedor a la vez" probado.</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="41.4" customHeight="1" s="19">
       <c r="A84" s="11" t="inlineStr">
@@ -6591,16 +6819,22 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I84" s="11" t="n"/>
-      <c r="J84" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J84" s="12" t="inlineStr">
+        <is>
+          <t>OrdenTrabajoAsignacion.aspx como modal (SigmaModal) desde la pestaña Asignación; la grilla se refresca al cerrar.</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="41.4" customHeight="1" s="19">
       <c r="A85" s="11" t="inlineStr">
@@ -6638,11 +6872,17 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I85" s="11" t="n"/>
-      <c r="J85" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J85" s="12" t="inlineStr">
+        <is>
+          <t>CREAR ORDEN TRABAJO en web (Menu_Funcion) y API (ExigirPermiso).</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="27.6" customHeight="1" s="19">
       <c r="A86" s="11" t="inlineStr">
@@ -6675,16 +6915,22 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I86" s="11" t="n"/>
-      <c r="J86" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J86" s="12" t="inlineStr">
+        <is>
+          <t>#1 técnico (web y API) · #2 empresa externa (SP OT-14) · #3 un solo responsable (API: [(11,True),(12,False)]) · #4 especialidad requerida (SP: advertencia en ota_observacion; OT-15 sin especialidad exigida → sin advertencia).</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="27.6" customHeight="1" s="19">
       <c r="A87" s="11" t="inlineStr">
@@ -6717,16 +6963,22 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I87" s="11" t="n"/>
-      <c r="J87" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J87" s="12" t="inlineStr">
+        <is>
+          <t>XML en el controlador; MD 10.10.</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="27.6" customHeight="1" s="19">
       <c r="A88" s="11" t="inlineStr">
@@ -6759,7 +7011,7 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
@@ -6770,7 +7022,7 @@
       <c r="I88" s="11" t="n"/>
       <c r="J88" s="12" t="inlineStr">
         <is>
-          <t>Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>No hecho en este bloque: la reasignación desde la app queda para la pantalla Flutter (el endpoint ya está).</t>
         </is>
       </c>
     </row>
@@ -8233,16 +8485,22 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I123" s="11" t="n"/>
-      <c r="J123" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>Índices existentes de Orden_Trabajo por cliente/estado alcanzan.</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="27.6" customHeight="1" s="19">
       <c r="A124" s="11" t="inlineStr">
@@ -8280,11 +8538,17 @@
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I124" s="11" t="n"/>
-      <c r="J124" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I124" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>Sin SP aparte: SEL_ORDEN_TRABAJO con @ESTADO=3 ordena por fecha de finalización y devuelve DIAS_ESPERA_CIERRE y PERMISOS_PENDIENTES; todo por parámetros, con paginación.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="27.6" customHeight="1" s="19">
       <c r="A125" s="11" t="inlineStr">
@@ -8317,16 +8581,22 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I125" s="11" t="n"/>
-      <c r="J125" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J125" s="12" t="inlineStr">
+        <is>
+          <t>Cubierto por los índices por cliente+estado ya existentes.</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="27.6" customHeight="1" s="19">
       <c r="A126" s="11" t="inlineStr">
@@ -8359,16 +8629,22 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I126" s="11" t="n"/>
-      <c r="J126" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J126" s="12" t="inlineStr">
+        <is>
+          <t>OT-2/3/4 en espera de cierre.</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="27.6" customHeight="1" s="19">
       <c r="A127" s="11" t="inlineStr">
@@ -8406,11 +8682,17 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I127" s="11" t="n"/>
-      <c r="J127" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J127" s="12" t="inlineStr">
+        <is>
+          <t>Sin pantalla suelta: OrdenTrabajos.aspx con estado «Bandeja de cierre» muestra días esperando y el cierre masivo con motivo común.</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="41.4" customHeight="1" s="19">
       <c r="A128" s="11" t="inlineStr">
@@ -8448,11 +8730,17 @@
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I128" s="11" t="n"/>
-      <c r="J128" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J128" s="12" t="inlineStr">
+        <is>
+          <t>Función «Cerrar» (CERRAR OT) en la página; el SP repite la validación por cada orden.</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="41.4" customHeight="1" s="19">
       <c r="A129" s="11" t="inlineStr">
@@ -8485,16 +8773,22 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I129" s="11" t="n"/>
-      <c r="J129" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J129" s="12" t="inlineStr">
+        <is>
+          <t>#1 bandeja ordenada por antigüedad con días (navegador) · #2 cierre desde la bandeja: 2 cerradas, 1 queda (navegador).</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="55.2" customHeight="1" s="19">
       <c r="A130" s="11" t="inlineStr">
@@ -8527,16 +8821,22 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I130" s="11" t="n"/>
-      <c r="J130" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J130" s="12" t="inlineStr">
+        <is>
+          <t>MD 10.10.</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="41.4" customHeight="1" s="19">
       <c r="A131" s="11" t="inlineStr">
@@ -9493,16 +9793,22 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I153" s="11" t="n"/>
-      <c r="J153" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I153" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J153" s="12" t="inlineStr">
+        <is>
+          <t>Falla: fal_activo_estado_posterior, fal_fecha_solucion_utc, fal_detuvo_produccion; Falla_Diagnostico (definitivo único), Falla_Accion (definitiva/provisoria).</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="55.2" customHeight="1" s="19">
       <c r="A154" s="11" t="inlineStr">
@@ -9535,16 +9841,22 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I154" s="11" t="n"/>
-      <c r="J154" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I154" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J154" s="12" t="inlineStr">
+        <is>
+          <t>BD/225 INS_FALLA: registra y, si trae estado posterior distinto del actual, llama a ACTIVO_CAMBIAR_ESTADO (historial del equipo).</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="41.4" customHeight="1" s="19">
       <c r="A155" s="11" t="inlineStr">
@@ -9582,11 +9894,17 @@
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I155" s="11" t="n"/>
-      <c r="J155" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I155" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J155" s="12" t="inlineStr">
+        <is>
+          <t>SEL_FALLA con contadores (diagnósticos, acciones, provisorias, órdenes, última OT, PROVISORIAS_DEL_EQUIPO) y filtro abiertas/resueltas.</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="41.4" customHeight="1" s="19">
       <c r="A156" s="11" t="inlineStr">
@@ -9619,16 +9937,22 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H156" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I156" s="11" t="n"/>
-      <c r="J156" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I156" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J156" s="12" t="inlineStr">
+        <is>
+          <t>UPD_FALLA: título, descripción, consecuencia, criticidad, detuvo producción; equipo/estado posterior se fijan al crear.</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="41.4" customHeight="1" s="19">
       <c r="A157" s="11" t="inlineStr">
@@ -9661,16 +9985,22 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I157" s="11" t="n"/>
-      <c r="J157" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I157" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J157" s="12" t="inlineStr">
+        <is>
+          <t>F-1 (web, ACT-34), F-2..F-5 (API, ACT-40).</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="41.4" customHeight="1" s="19">
       <c r="A158" s="11" t="inlineStr">
@@ -9708,11 +10038,17 @@
       </c>
       <c r="H158" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I158" s="11" t="n"/>
-      <c r="J158" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I158" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" s="12" t="inlineStr">
+        <is>
+          <t>POST /fallas; POST /fallas/{id}/diagnosticos; POST /fallas/{id}/acciones; POST /fallas/{id}/orden.</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="27.6" customHeight="1" s="19">
       <c r="A159" s="11" t="inlineStr">
@@ -9745,16 +10081,22 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I159" s="11" t="n"/>
-      <c r="J159" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I159" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J159" s="12" t="inlineStr">
+        <is>
+          <t>GET /fallas, /fallas/{id}, /{id}/diagnosticos, /{id}/acciones.</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="27.6" customHeight="1" s="19">
       <c r="A160" s="11" t="inlineStr">
@@ -9792,11 +10134,17 @@
       </c>
       <c r="H160" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I160" s="11" t="n"/>
-      <c r="J160" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I160" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J160" s="12" t="inlineStr">
+        <is>
+          <t>FallaAltaDto / FallaDiagnosticoAltaDto / FallaAccionAltaDto; ExigirCuerpo.</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="27.6" customHeight="1" s="19">
       <c r="A161" s="11" t="inlineStr">
@@ -9829,16 +10177,22 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I161" s="11" t="n"/>
-      <c r="J161" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I161" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J161" s="12" t="inlineStr">
+        <is>
+          <t>Falla.aspx: centro con pestañas Ficha / Diagnósticos / Acciones / Indisponibilidad y «Generar orden correctiva».</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="41.4" customHeight="1" s="19">
       <c r="A162" s="11" t="inlineStr">
@@ -9876,11 +10230,17 @@
       </c>
       <c r="H162" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I162" s="11" t="n"/>
-      <c r="J162" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I162" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" s="12" t="inlineStr">
+        <is>
+          <t>Fallas.aspx: situación (abierta / diagnosticada / provisoria / resuelta), OT, historial de provisorias del equipo.</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="27.6" customHeight="1" s="19">
       <c r="A163" s="11" t="inlineStr">
@@ -9922,7 +10282,11 @@
         </is>
       </c>
       <c r="I163" s="11" t="n"/>
-      <c r="J163" s="12" t="n"/>
+      <c r="J163" s="12" t="inlineStr">
+        <is>
+          <t>No hecho en este bloque: la pantalla Flutter de fallas queda pendiente (endpoints listos).</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="27.6" customHeight="1" s="19">
       <c r="A164" s="11" t="inlineStr">
@@ -9955,16 +10319,22 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H164" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I164" s="11" t="n"/>
-      <c r="J164" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I164" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J164" s="12" t="inlineStr">
+        <is>
+          <t>Permiso nuevo REGISTRAR FALLA (perfiles 5,11,12,13); Menus + Menu_Funcion «Crear y editar».</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="27.6" customHeight="1" s="19">
       <c r="A165" s="11" t="inlineStr">
@@ -9997,16 +10367,22 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I165" s="11" t="n"/>
-      <c r="J165" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I165" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" s="12" t="inlineStr">
+        <is>
+          <t>#1 registro (web F-1, API 201) · #2 diagnóstico posterior con un solo definitivo (API) · #3 provisoria mantiene abierta / definitiva resuelve (web y API) · #4 estado posterior: ACT-34 quedó Detenido con historial.</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="27.6" customHeight="1" s="19">
       <c r="A166" s="11" t="inlineStr">
@@ -10039,16 +10415,22 @@
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H166" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I166" s="11" t="n"/>
-      <c r="J166" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I166" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J166" s="12" t="inlineStr">
+        <is>
+          <t>XML en FallasController; MD 10.10.</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="55.2" customHeight="1" s="19">
       <c r="A167" s="11" t="inlineStr">
@@ -10081,16 +10463,22 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I167" s="11" t="n"/>
-      <c r="J167" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I167" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J167" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente de la PO; la historia queda En revisión.</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="41.4" customHeight="1" s="19">
       <c r="A168" s="11" t="inlineStr">
@@ -10128,11 +10516,17 @@
       </c>
       <c r="H168" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I168" s="11" t="n"/>
-      <c r="J168" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I168" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J168" s="12" t="inlineStr">
+        <is>
+          <t>Activo_Indisponibilidad: ain_minuto, ain_planificada, ain_detuvo_produccion, motivo de catálogo o texto; orden y falla opcionales.</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="41.4" customHeight="1" s="19">
       <c r="A169" s="11" t="inlineStr">
@@ -10165,16 +10559,22 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I169" s="11" t="n"/>
-      <c r="J169" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I169" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J169" s="12" t="inlineStr">
+        <is>
+          <t>BD/225 INS_ACTIVO_INDISPONIBILIDAD: minutos calculados, término no anterior al inicio, motivo obligatorio (catálogo o texto).</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="27.6" customHeight="1" s="19">
       <c r="A170" s="11" t="inlineStr">
@@ -10207,16 +10607,22 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H170" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I170" s="11" t="n"/>
-      <c r="J170" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I170" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J170" s="12" t="inlineStr">
+        <is>
+          <t>SEL_ACTIVO_INDISPONIBILIDAD con MINUTOS_ACUMULADOS (abierta: corre contra la hora del servidor).</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="27.6" customHeight="1" s="19">
       <c r="A171" s="11" t="inlineStr">
@@ -10254,11 +10660,17 @@
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I171" s="11" t="n"/>
-      <c r="J171" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I171" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J171" s="12" t="inlineStr">
+        <is>
+          <t>UPD_ACTIVO_INDISPONIBILIDAD: cerrar el periodo o corregir tipo y motivo.</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="27.6" customHeight="1" s="19">
       <c r="A172" s="11" t="inlineStr">
@@ -10291,16 +10703,22 @@
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H172" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I172" s="11" t="n"/>
-      <c r="J172" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I172" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J172" s="12" t="inlineStr">
+        <is>
+          <t>Indisponibilidades 1 (web, OT-15, 210 min) y 2..7 (API).</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="27.6" customHeight="1" s="19">
       <c r="A173" s="11" t="inlineStr">
@@ -10333,16 +10751,22 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I173" s="11" t="n"/>
-      <c r="J173" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I173" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J173" s="12" t="inlineStr">
+        <is>
+          <t>POST /activo-indisponibilidades.</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="27.6" customHeight="1" s="19">
       <c r="A174" s="11" t="inlineStr">
@@ -10380,11 +10804,17 @@
       </c>
       <c r="H174" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I174" s="11" t="n"/>
-      <c r="J174" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I174" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J174" s="12" t="inlineStr">
+        <is>
+          <t>GET /activo-indisponibilidades y /{id}; PUT /{id}.</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="27.6" customHeight="1" s="19">
       <c r="A175" s="11" t="inlineStr">
@@ -10417,16 +10847,22 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I175" s="11" t="n"/>
-      <c r="J175" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I175" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J175" s="12" t="inlineStr">
+        <is>
+          <t>ActivoIndisponibilidadAltaDto / EdicionDto.</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="27.6" customHeight="1" s="19">
       <c r="A176" s="11" t="inlineStr">
@@ -10459,16 +10895,22 @@
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H176" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I176" s="11" t="n"/>
-      <c r="J176" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I176" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J176" s="12" t="inlineStr">
+        <is>
+          <t>ActivoIndisponibilidad.aspx como modal desde la OT y desde la falla (equipo, orden y falla vienen cifrados en el query).</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="27.6" customHeight="1" s="19">
       <c r="A177" s="11" t="inlineStr">
@@ -10506,11 +10948,17 @@
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I177" s="11" t="n"/>
-      <c r="J177" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I177" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J177" s="12" t="inlineStr">
+        <is>
+          <t>Sin listado suelto: pestaña Indisponibilidad en la OT y en la falla, con minutos y tipo.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
@@ -10543,7 +10991,7 @@
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H178" s="11" t="inlineStr">
@@ -10552,7 +11000,11 @@
         </is>
       </c>
       <c r="I178" s="11" t="n"/>
-      <c r="J178" s="12" t="n"/>
+      <c r="J178" s="12" t="inlineStr">
+        <is>
+          <t>No hecho en este bloque: consumo desde la app pendiente (endpoints listos).</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="55.2" customHeight="1" s="19">
       <c r="A179" s="11" t="inlineStr">
@@ -10590,11 +11042,17 @@
       </c>
       <c r="H179" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I179" s="11" t="n"/>
-      <c r="J179" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I179" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J179" s="12" t="inlineStr">
+        <is>
+          <t>REGISTRAR FALLA en web y API; @CLIENTE en todos los SP.</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="41.4" customHeight="1" s="19">
       <c r="A180" s="11" t="inlineStr">
@@ -10627,16 +11085,22 @@
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H180" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I180" s="11" t="n"/>
-      <c r="J180" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I180" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J180" s="12" t="inlineStr">
+        <is>
+          <t>#1 registro con minutos calculados (web 210, API 105) · #2 planificada / no planificada (API) · #3 sin orden ni falla, abierta (API 201). Término anterior al inicio → 400.</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="55.2" customHeight="1" s="19">
       <c r="A181" s="11" t="inlineStr">
@@ -10669,16 +11133,22 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H181" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I181" s="11" t="n"/>
-      <c r="J181" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I181" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J181" s="12" t="inlineStr">
+        <is>
+          <t>XML en IndisponibilidadesController; MD 10.10.</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="41.4" customHeight="1" s="19">
       <c r="A182" s="11" t="inlineStr">
@@ -16595,7 +17065,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16628,7 +17098,7 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16661,7 +17131,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16693,7 +17163,7 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17078,7 +17548,7 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17580,7 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17143,7 +17613,7 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17174,7 +17644,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17301,7 +17771,7 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17333,7 +17803,7 @@
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17365,7 +17835,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17397,7 +17867,7 @@
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17718,7 +18188,7 @@
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17750,7 +18220,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17970,7 +18440,7 @@
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18472,7 @@
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18504,7 @@
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18065,7 +18535,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18096,7 +18566,7 @@
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18128,7 +18598,7 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18629,7 @@
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
@@ -1430,11 +1430,19 @@
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O7" s="14" t="n"/>
-      <c r="P7" s="14" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O7" s="14" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P7" s="14" t="inlineStr">
+        <is>
+          <t>A nombre de Bryan (14-09-2026). Ya estaba construida; hoy la regla de obligatorios pasó al SP (BD/227). Pendiente validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="69" customHeight="1" s="19">
       <c r="A8" s="11" t="inlineStr">
@@ -1714,13 +1722,17 @@
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P11" s="14" t="inlineStr">
         <is>
-          <t>· ALCANCE APP (30-08): App y Web → App. Solo App (R3): es SU bandeja. La de supervision es HU-122 (web).</t>
+          <t>A nombre de Bryan (14-09-2026). Ya estaba construida; verificada por HTTP hoy.</t>
         </is>
       </c>
     </row>
@@ -1860,11 +1872,19 @@
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O13" s="14" t="n"/>
-      <c r="P13" s="14" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P13" s="14" t="inlineStr">
+        <is>
+          <t>A nombre de Bryan (14-09-2026). Ya estaba construida en la app; verificada por HTTP hoy (probar_ot_app.py). Pendiente validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="69" customHeight="1" s="19">
       <c r="A14" s="11" t="inlineStr">
@@ -1927,13 +1947,17 @@
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>· ALCANCE APP (30-08): App y Web → App. Solo App (R3): el tecnico consume. La entrega de bodega es HU-055.</t>
+          <t>A nombre de Bryan (14-09-2026). Ya estaba construida; hoy se destrabó el consumo del técnico (ubicaciones de bodega).</t>
         </is>
       </c>
     </row>
@@ -1998,13 +2022,17 @@
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O15" s="14" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O15" s="14" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>· ALCANCE APP (30-08): App y Web → App. Solo App (R3): finalizar es del tecnico. Cerrar es HU-120 (web).</t>
+          <t>A nombre de Bryan (14-09-2026). BD/227: obligatorios pendientes rechazados con nombres, resultado y fecha fin real, advertencia sin mano de obra.</t>
         </is>
       </c>
     </row>
@@ -2144,13 +2172,17 @@
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O17" s="14" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O17" s="14" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>· ALCANCE APP (30-08): Web y App → App. Solo App (R3): el tecnico registra sus horas. La validacion es HU-118.</t>
+          <t>A nombre de Bryan (14-09-2026). Ya estaba construida; hoy el ejecutante inválido se rechaza con mensaje (BD/227).</t>
         </is>
       </c>
     </row>
@@ -2637,11 +2669,19 @@
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P24" s="12" t="inlineStr">
+        <is>
+          <t>A nombre de Bryan (14-09-2026). Firmas desde la app; sin pantalla web propia (T-5244/5245 quedan Por hacer).</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55.2" customHeight="1" s="19">
       <c r="A25" s="13" t="inlineStr">
@@ -3790,13 +3830,15 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>No aplica en este bloque: el alta desde el teléfono ya existía (HU-110 app).</t>
+          <t>Ya existía (nueva_orden_screen, encolada con uuid). Hoy además la correctiva nace desde la ficha de la falla (POST /fallas/{id}/orden).</t>
         </is>
       </c>
     </row>
@@ -4023,16 +4065,22 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>Orden_Trabajo_Paso: otp_obligatorio, otp_resultado_paso (4 PENDIENTE), otp_uuid con UQ_OTP_UUID (BD/209).</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="27.6" customHeight="1" s="19">
       <c r="A22" s="11" t="inlineStr">
@@ -4070,11 +4118,17 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="n"/>
-      <c r="J22" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>Los pasos viajan dentro de GET /ordenes-trabajo/{id} (API_SEL_ORDEN_TRABAJO_PASO), acotados al cliente y las plantas del usuario.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="41.4" customHeight="1" s="19">
       <c r="A23" s="11" t="inlineStr">
@@ -4107,16 +4161,22 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>API_INS_ORDEN_TRABAJO_PASO idempotente por uuid (BD/209); el resultado de un paso por API_UPD_ORDEN_TRABAJO_PASO.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="27.6" customHeight="1" s="19">
       <c r="A24" s="11" t="inlineStr">
@@ -4149,16 +4209,22 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="n"/>
-      <c r="J24" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>OT-27..32 creadas desde la app con dos pasos obligatorios cada una.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="27.6" customHeight="1" s="19">
       <c r="A25" s="11" t="inlineStr">
@@ -4191,16 +4257,22 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="n"/>
-      <c r="J25" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>Sin endpoint /sync aparte: la ficha completa baja en un viaje y la sábana (bloque ORDENES_TRABAJO) cubre el offline.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="27.6" customHeight="1" s="19">
       <c r="A26" s="11" t="inlineStr">
@@ -4238,11 +4310,17 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="n"/>
-      <c r="J26" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>POST /ordenes-trabajo/pasos/{id} y POST /ordenes-trabajo/{id}/pasos, idempotentes por uuid, salen de la cola (outbox) uno a uno.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="41.4" customHeight="1" s="19">
       <c r="A27" s="11" t="inlineStr">
@@ -4275,16 +4353,22 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía: FNC_SUSCRIPCION_VIGENTE → 402 en ApiBase.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="27.6" customHeight="1" s="19">
       <c r="A28" s="11" t="inlineStr">
@@ -4317,16 +4401,22 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="n"/>
-      <c r="J28" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>orden_ficha_screen + hoja_paso: pestaña Pasos con objetivos grandes, conforme / no conforme / no aplica con comentario.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="27.6" customHeight="1" s="19">
       <c r="A29" s="11" t="inlineStr">
@@ -4364,11 +4454,17 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>OutboxService: SQLite primero, uuid al encolar; PASO en la cola.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="27.6" customHeight="1" s="19">
       <c r="A30" s="11" t="inlineStr">
@@ -4401,16 +4497,22 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="n"/>
-      <c r="J30" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>Reintento con el mismo uuid → misma respuesta (probado: reintento del alta devuelve el mismo id).</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="27.6" customHeight="1" s="19">
       <c r="A31" s="11" t="inlineStr">
@@ -4443,16 +4545,22 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="n"/>
-      <c r="J31" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>EJECUTAR ORDEN TRABAJO en el endpoint; el SP exige estar asignado y la OT en ejecución.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55.2" customHeight="1" s="19">
       <c r="A32" s="11" t="inlineStr">
@@ -4485,16 +4593,22 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="n"/>
-      <c r="J32" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>#1 conforme con ejecutor y hora · #2 no aplica con comentario · #3 obligatorio pendiente: ahora lo rechaza el SP y nombra los pasos (BD/227) · #4 medición: queda en la serie del activo vía /captura/mediciones (HU-043) · #5 offline: cola verificada en sesiones anteriores.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="41.4" customHeight="1" s="19">
       <c r="A33" s="11" t="inlineStr">
@@ -4527,16 +4641,22 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I33" s="11" t="n"/>
-      <c r="J33" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>XML en OrdenesTrabajoController; MD 10.11.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="41.4" customHeight="1" s="19">
       <c r="A34" s="11" t="inlineStr">
@@ -4569,16 +4689,22 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I34" s="11" t="n"/>
-      <c r="J34" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente de la PO; historia En revisión.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="27.6" customHeight="1" s="19">
       <c r="A35" s="11" t="inlineStr">
@@ -6063,16 +6189,22 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I67" s="11" t="n"/>
-      <c r="J67" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J67" s="12" t="inlineStr">
+        <is>
+          <t>Índices por cliente+estado existentes.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="27.6" customHeight="1" s="19">
       <c r="A68" s="11" t="inlineStr">
@@ -6110,11 +6242,17 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="n"/>
-      <c r="J68" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J68" s="12" t="inlineStr">
+        <is>
+          <t>API_SEL_ORDEN_TRABAJO_BANDEJA con @AMBITO 1/2/3, SITUACION (VENCIDA / VENCE HOY / EN PLAZO) calculada en el SP.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="41.4" customHeight="1" s="19">
       <c r="A69" s="11" t="inlineStr">
@@ -6147,16 +6285,22 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="n"/>
-      <c r="J69" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J69" s="12" t="inlineStr">
+        <is>
+          <t>Cubierto por los índices existentes.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="55.2" customHeight="1" s="19">
       <c r="A70" s="11" t="inlineStr">
@@ -6189,16 +6333,22 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="n"/>
-      <c r="J70" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>OT-27..32 de prueba; bandeja de Cristián con 5 y disponibles 10.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="41.4" customHeight="1" s="19">
       <c r="A71" s="11" t="inlineStr">
@@ -6231,16 +6381,22 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I71" s="11" t="n"/>
-      <c r="J71" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J71" s="12" t="inlineStr">
+        <is>
+          <t>GET /ordenes-trabajo?ambito=&amp;instalacion=&amp;desde= (paginado en el SP).</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="41.4" customHeight="1" s="19">
       <c r="A72" s="11" t="inlineStr">
@@ -6278,11 +6434,17 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I72" s="11" t="n"/>
-      <c r="J72" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J72" s="12" t="inlineStr">
+        <is>
+          <t>No hay caché en servidor: la app guarda la última bandeja en SQLite (sábana) y la muestra sin señal, que es lo que pide el criterio 2.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="27.6" customHeight="1" s="19">
       <c r="A73" s="11" t="inlineStr">
@@ -6315,16 +6477,22 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I73" s="11" t="n"/>
-      <c r="J73" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J73" s="12" t="inlineStr">
+        <is>
+          <t>ordenes_screen.dart: pestañas Mías / Disponibles / Planta; mi_trabajo_screen une órdenes, tareas y pautas.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="41.4" customHeight="1" s="19">
       <c r="A74" s="11" t="inlineStr">
@@ -6357,16 +6525,22 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="n"/>
-      <c r="J74" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J74" s="12" t="inlineStr">
+        <is>
+          <t>VER ORDENES TRABAJO; el SP filtra por cliente y plantas del usuario.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="27.6" customHeight="1" s="19">
       <c r="A75" s="11" t="inlineStr">
@@ -6399,16 +6573,22 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="n"/>
-      <c r="J75" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J75" s="12" t="inlineStr">
+        <is>
+          <t>#1 bandeja con SITUACION (HTTP) · #2 sin conexión desde la sábana (verificado en sesiones anteriores, bloque ORDENES_TRABAJO) · #3 disponibles: la OT nueva aparece sin dueño (HTTP).</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="27.6" customHeight="1" s="19">
       <c r="A76" s="11" t="inlineStr">
@@ -6441,16 +6621,22 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="n"/>
-      <c r="J76" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J76" s="12" t="inlineStr">
+        <is>
+          <t>MD 10.11.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="27.6" customHeight="1" s="19">
       <c r="A77" s="11" t="inlineStr">
@@ -7016,13 +7202,15 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I88" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I88" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J88" s="12" t="inlineStr">
         <is>
-          <t>No hecho en este bloque: la reasignación desde la app queda para la pantalla Flutter (el endpoint ya está).</t>
+          <t>hoja_asignar.dart: responsable o apoyo desde la ficha de la OT, con la gente de la planta; encolada con uuid (BD/226).</t>
         </is>
       </c>
     </row>
@@ -7057,16 +7245,22 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I89" s="11" t="n"/>
-      <c r="J89" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J89" s="12" t="inlineStr">
+        <is>
+          <t>Orden_Trabajo_Asignacion con UX_OTA_RESPONSABLE filtrado.</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="27.6" customHeight="1" s="19">
       <c r="A90" s="11" t="inlineStr">
@@ -7104,11 +7298,17 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I90" s="11" t="n"/>
-      <c r="J90" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I90" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J90" s="12" t="inlineStr">
+        <is>
+          <t>API_UPD_ORDEN_TRABAJO_TOMAR: UPDATE … WHERE estado = 1 con @@ROWCOUNT (la carrera se resuelve en la base).</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="41.4" customHeight="1" s="19">
       <c r="A91" s="11" t="inlineStr">
@@ -7141,16 +7341,22 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I91" s="11" t="n"/>
-      <c r="J91" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J91" s="12" t="inlineStr">
+        <is>
+          <t>La regla vive en el SP; web y app reciben el mismo veredicto.</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="55.2" customHeight="1" s="19">
       <c r="A92" s="11" t="inlineStr">
@@ -7183,16 +7389,22 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="n"/>
-      <c r="J92" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J92" s="12" t="inlineStr">
+        <is>
+          <t>El resultado se lee en GET /ordenes-trabajo/{id} (estado y asignados).</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="41.4" customHeight="1" s="19">
       <c r="A93" s="11" t="inlineStr">
@@ -7230,11 +7442,17 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I93" s="11" t="n"/>
-      <c r="J93" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J93" s="12" t="inlineStr">
+        <is>
+          <t>OT-29: Cristián toma, Paula llega segunda.</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="41.4" customHeight="1" s="19">
       <c r="A94" s="11" t="inlineStr">
@@ -7267,16 +7485,22 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I94" s="11" t="n"/>
-      <c r="J94" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J94" s="12" t="inlineStr">
+        <is>
+          <t>POST /ordenes-trabajo/{id}/tomar.</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="41.4" customHeight="1" s="19">
       <c r="A95" s="11" t="inlineStr">
@@ -7314,11 +7538,17 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I95" s="11" t="n"/>
-      <c r="J95" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J95" s="12" t="inlineStr">
+        <is>
+          <t>«La orden ya fue tomada por otro usuario o no está abierta» llega como 400 de negocio con mensaje, no como 500.</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="41.4" customHeight="1" s="19">
       <c r="A96" s="11" t="inlineStr">
@@ -7356,11 +7586,17 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I96" s="11" t="n"/>
-      <c r="J96" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J96" s="12" t="inlineStr">
+        <is>
+          <t>Botón «Tomar trabajo» en la ficha; arranca el cronómetro.</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="27.6" customHeight="1" s="19">
       <c r="A97" s="11" t="inlineStr">
@@ -7393,16 +7629,22 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I97" s="11" t="n"/>
-      <c r="J97" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J97" s="12" t="inlineStr">
+        <is>
+          <t>TOMAR ORDEN TRABAJO en el endpoint.</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="27.6" customHeight="1" s="19">
       <c r="A98" s="11" t="inlineStr">
@@ -7435,16 +7677,22 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I98" s="11" t="n"/>
-      <c r="J98" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J98" s="12" t="inlineStr">
+        <is>
+          <t>#1 toma → EN EJECUCION y responsable · #2 dos técnicos: el segundo recibe «ya fue tomada» · #3 sumar compañero: dos asignados, un responsable (POST asignaciones con es_responsable=false).</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="27.6" customHeight="1" s="19">
       <c r="A99" s="11" t="inlineStr">
@@ -7477,16 +7725,22 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I99" s="11" t="n"/>
-      <c r="J99" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J99" s="12" t="inlineStr">
+        <is>
+          <t>MD 10.11.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="27.6" customHeight="1" s="19">
       <c r="A100" s="11" t="inlineStr">
@@ -7519,16 +7773,22 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I100" s="11" t="n"/>
-      <c r="J100" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>Orden_Trabajo_Repuesto: consumida / devuelta / costo unitario; uuid del movimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="27.6" customHeight="1" s="19">
       <c r="A101" s="11" t="inlineStr">
@@ -7561,16 +7821,22 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I101" s="11" t="n"/>
-      <c r="J101" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J101" s="12" t="inlineStr">
+        <is>
+          <t>API_INS_ORDEN_TRABAJO_REPUESTO mueve inventario y orden en una transacción; exige ubicación si la bodega las tiene.</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="41.4" customHeight="1" s="19">
       <c r="A102" s="11" t="inlineStr">
@@ -7608,11 +7874,17 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I102" s="11" t="n"/>
-      <c r="J102" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J102" s="12" t="inlineStr">
+        <is>
+          <t>GET /ordenes-trabajo/{id}/recursos (repuestos con consumido y devuelto) y /repuestos-disponibles con ES_COMPATIBLE.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="27.6" customHeight="1" s="19">
       <c r="A103" s="11" t="inlineStr">
@@ -7645,16 +7917,22 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I103" s="11" t="n"/>
-      <c r="J103" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J103" s="12" t="inlineStr">
+        <is>
+          <t>No hay UPD: consumo y devolución son movimientos (append), la corrección es una devolución.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="55.2" customHeight="1" s="19">
       <c r="A104" s="11" t="inlineStr">
@@ -7687,16 +7965,22 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I104" s="11" t="n"/>
-      <c r="J104" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J104" s="12" t="inlineStr">
+        <is>
+          <t>REP-6205 en Bodega Frío: consumido 1 y devuelto 1 sobre OT-31.</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="41.4" customHeight="1" s="19">
       <c r="A105" s="11" t="inlineStr">
@@ -7729,16 +8013,22 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I105" s="11" t="n"/>
-      <c r="J105" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J105" s="12" t="inlineStr">
+        <is>
+          <t>POST /ordenes-trabajo/{id}/repuestos idempotente por uuid (reintento no consume dos veces).</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="41.4" customHeight="1" s="19">
       <c r="A106" s="11" t="inlineStr">
@@ -7776,11 +8066,17 @@
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I106" s="11" t="n"/>
-      <c r="J106" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J106" s="12" t="inlineStr">
+        <is>
+          <t>Cubierto por /recursos y /repuestos-disponibles.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="41.4" customHeight="1" s="19">
       <c r="A107" s="11" t="inlineStr">
@@ -7813,16 +8109,22 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I107" s="11" t="n"/>
-      <c r="J107" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J107" s="12" t="inlineStr">
+        <is>
+          <t>OrdenTrabajoRepuestoAltaDto; ExigirCuerpo.</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="41.4" customHeight="1" s="19">
       <c r="A108" s="11" t="inlineStr">
@@ -7855,16 +8157,22 @@
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I108" s="11" t="n"/>
-      <c r="J108" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J108" s="12" t="inlineStr">
+        <is>
+          <t>hojas_recursos.dart: consumo y devolución con bodega y estante. Defecto corregido hoy: GET /bodegas/{id}/ubicaciones daba 403 al técnico (VER BODEGAS) y dejaba el consumo sin camino; ahora acepta EJECUTAR ORDEN TRABAJO.</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="27.6" customHeight="1" s="19">
       <c r="A109" s="11" t="inlineStr">
@@ -7902,11 +8210,17 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I109" s="11" t="n"/>
-      <c r="J109" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>EJECUTAR ORDEN TRABAJO; cliente del token.</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="27.6" customHeight="1" s="19">
       <c r="A110" s="11" t="inlineStr">
@@ -7939,16 +8253,22 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I110" s="11" t="n"/>
-      <c r="J110" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J110" s="12" t="inlineStr">
+        <is>
+          <t>#1 consumo descuenta y suma costo (SP en transacción) · #2 horómetro de la pieza: campos opcionales del DTO (no verificado con datos) · #3 devolución: consumido 0, devuelto 1.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="27.6" customHeight="1" s="19">
       <c r="A111" s="11" t="inlineStr">
@@ -7981,16 +8301,22 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I111" s="11" t="n"/>
-      <c r="J111" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J111" s="12" t="inlineStr">
+        <is>
+          <t>MD 10.11.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="41.4" customHeight="1" s="19">
       <c r="A112" s="11" t="inlineStr">
@@ -8028,11 +8354,17 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I112" s="11" t="n"/>
-      <c r="J112" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J112" s="12" t="inlineStr">
+        <is>
+          <t>otr_resultado, otr_fecha_fin_real_utc, otr_duracion_real_minuto.</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="27.6" customHeight="1" s="19">
       <c r="A113" s="11" t="inlineStr">
@@ -8065,16 +8397,22 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I113" s="11" t="n"/>
-      <c r="J113" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J113" s="12" t="inlineStr">
+        <is>
+          <t>BD/227 UPD_ORDEN_TRABAJO_FINALIZAR: rechaza con los nombres de los obligatorios pendientes, guarda resultado y fecha fin real, advierte sin mano de obra.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="27.6" customHeight="1" s="19">
       <c r="A114" s="11" t="inlineStr">
@@ -8107,16 +8445,22 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I114" s="11" t="n"/>
-      <c r="J114" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J114" s="12" t="inlineStr">
+        <is>
+          <t>La regla pasó del botón de la app al SP: probado por HTTP que antes el endpoint dejaba finalizar con obligatorios pendientes.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="27.6" customHeight="1" s="19">
       <c r="A115" s="11" t="inlineStr">
@@ -8154,11 +8498,17 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I115" s="11" t="n"/>
-      <c r="J115" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J115" s="12" t="inlineStr">
+        <is>
+          <t>El SP devuelve ORDEN_TRABAJO, ESTADO, ADVERTENCIA; la API la expone como `advertencia`.</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="27.6" customHeight="1" s="19">
       <c r="A116" s="11" t="inlineStr">
@@ -8191,16 +8541,22 @@
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I116" s="11" t="n"/>
-      <c r="J116" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J116" s="12" t="inlineStr">
+        <is>
+          <t>OT-29..32.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="27.6" customHeight="1" s="19">
       <c r="A117" s="11" t="inlineStr">
@@ -8238,11 +8594,17 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I117" s="11" t="n"/>
-      <c r="J117" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J117" s="12" t="inlineStr">
+        <is>
+          <t>POST /ordenes-trabajo/{id}/finalizar → 200 {otr_id, advertencia}.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="55.2" customHeight="1" s="19">
       <c r="A118" s="11" t="inlineStr">
@@ -8275,16 +8637,22 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I118" s="11" t="n"/>
-      <c r="J118" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I118" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J118" s="12" t="inlineStr">
+        <is>
+          <t>«Faltan pasos obligatorios por resolver: Revisar rodamiento, Medir vibración» → 400 con mensaje.</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="41.4" customHeight="1" s="19">
       <c r="A119" s="11" t="inlineStr">
@@ -8322,11 +8690,17 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I119" s="11" t="n"/>
-      <c r="J119" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J119" s="12" t="inlineStr">
+        <is>
+          <t>orden_ficha_screen: diálogo de resultado, tiempo del cronómetro como mano de obra, y la advertencia del servidor en pantalla.</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="41.4" customHeight="1" s="19">
       <c r="A120" s="11" t="inlineStr">
@@ -8359,16 +8733,22 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I120" s="11" t="n"/>
-      <c r="J120" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J120" s="12" t="inlineStr">
+        <is>
+          <t>EJECUTAR ORDEN TRABAJO.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="27.6" customHeight="1" s="19">
       <c r="A121" s="11" t="inlineStr">
@@ -8401,16 +8781,22 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I121" s="11" t="n"/>
-      <c r="J121" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I121" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J121" s="12" t="inlineStr">
+        <is>
+          <t>#1 finaliza → EN ESPERA DE CIERRE y no se modifica (paso rechazado) · #2 obligatorios pendientes → 400 con nombres · #3 sin mano de obra → advertencia y se permite (SP).</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="41.4" customHeight="1" s="19">
       <c r="A122" s="11" t="inlineStr">
@@ -8443,16 +8829,22 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I122" s="11" t="n"/>
-      <c r="J122" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I122" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>MD 10.11.</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="27.6" customHeight="1" s="19">
       <c r="A123" s="11" t="inlineStr">
@@ -8874,11 +9266,17 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I131" s="11" t="n"/>
-      <c r="J131" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I131" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>Orden_Trabajo_Mano_Obra: usuario o proveedor, minutos, costo hora y moneda, uuid.</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="41.4" customHeight="1" s="19">
       <c r="A132" s="11" t="inlineStr">
@@ -8911,16 +9309,22 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I132" s="11" t="n"/>
-      <c r="J132" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J132" s="12" t="inlineStr">
+        <is>
+          <t>API_INS_ORDEN_TRABAJO_MANO_OBRA (BD/193) + BD/227: el ejecutante se valida antes de insertar.</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="27.6" customHeight="1" s="19">
       <c r="A133" s="11" t="inlineStr">
@@ -8953,16 +9357,22 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I133" s="11" t="n"/>
-      <c r="J133" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J133" s="12" t="inlineStr">
+        <is>
+          <t>GET /ordenes-trabajo/{id}/recursos.</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="41.4" customHeight="1" s="19">
       <c r="A134" s="11" t="inlineStr">
@@ -9000,11 +9410,17 @@
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I134" s="11" t="n"/>
-      <c r="J134" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J134" s="12" t="inlineStr">
+        <is>
+          <t>Append-only: no hay UPD, se corrige agregando otro tramo.</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="27.6" customHeight="1" s="19">
       <c r="A135" s="11" t="inlineStr">
@@ -9037,16 +9453,22 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I135" s="11" t="n"/>
-      <c r="J135" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J135" s="12" t="inlineStr">
+        <is>
+          <t>Tramo de 90 min sobre OT-29..32.</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="27.6" customHeight="1" s="19">
       <c r="A136" s="11" t="inlineStr">
@@ -9084,11 +9506,17 @@
       </c>
       <c r="H136" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I136" s="11" t="n"/>
-      <c r="J136" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J136" s="12" t="inlineStr">
+        <is>
+          <t>POST /ordenes-trabajo/{id}/mano-obra idempotente por uuid.</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="27.6" customHeight="1" s="19">
       <c r="A137" s="11" t="inlineStr">
@@ -9121,16 +9549,22 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I137" s="11" t="n"/>
-      <c r="J137" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J137" s="12" t="inlineStr">
+        <is>
+          <t>Cubierto por /recursos.</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="27.6" customHeight="1" s="19">
       <c r="A138" s="11" t="inlineStr">
@@ -9168,11 +9602,17 @@
       </c>
       <c r="H138" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I138" s="11" t="n"/>
-      <c r="J138" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J138" s="12" t="inlineStr">
+        <is>
+          <t>ManoObraAltaDto.</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="27.6" customHeight="1" s="19">
       <c r="A139" s="11" t="inlineStr">
@@ -9205,16 +9645,22 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I139" s="11" t="n"/>
-      <c r="J139" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J139" s="12" t="inlineStr">
+        <is>
+          <t>hojas_recursos.dart (tramo manual) y cronómetro que se anota al finalizar.</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="55.2" customHeight="1" s="19">
       <c r="A140" s="11" t="inlineStr">
@@ -9247,16 +9693,22 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H140" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I140" s="11" t="n"/>
-      <c r="J140" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J140" s="12" t="inlineStr">
+        <is>
+          <t>EJECUTAR ORDEN TRABAJO; plantas del usuario.</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="41.4" customHeight="1" s="19">
       <c r="A141" s="11" t="inlineStr">
@@ -9289,16 +9741,22 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I141" s="11" t="n"/>
-      <c r="J141" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I141" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J141" s="12" t="inlineStr">
+        <is>
+          <t>#1 minutos calculados = 90 y duración real = suma · #2 externa: proveedor y valor hora en el modelo (no verificado con datos de proveedor) · #3 sin ejecutante válido → rechazado con mensaje (antes FK cruda).</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="41.4" customHeight="1" s="19">
       <c r="A142" s="11" t="inlineStr">
@@ -9331,16 +9789,22 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H142" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I142" s="11" t="n"/>
-      <c r="J142" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J142" s="12" t="inlineStr">
+        <is>
+          <t>MD 10.11.</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="41.4" customHeight="1" s="19">
       <c r="A143" s="11" t="inlineStr">
@@ -10278,13 +10742,15 @@
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I163" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I163" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J163" s="12" t="inlineStr">
         <is>
-          <t>No hecho en este bloque: la pantalla Flutter de fallas queda pendiente (endpoints listos).</t>
+          <t>fallas_screen / nueva_falla_screen / falla_ficha_screen: registrar, diagnósticos, acciones, parada y abrir la correctiva; menú app://fallas; todo encolado con uuid (BD/226).</t>
         </is>
       </c>
     </row>
@@ -10996,13 +11462,15 @@
       </c>
       <c r="H178" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I178" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I178" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J178" s="12" t="inlineStr">
         <is>
-          <t>No hecho en este bloque: consumo desde la app pendiente (endpoints listos).</t>
+          <t>hoja_indisponibilidad.dart desde la OT y desde la falla; encolada con uuid (BD/226).</t>
         </is>
       </c>
     </row>
@@ -12777,16 +13245,22 @@
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H220" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I220" s="11" t="n"/>
-      <c r="J220" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I220" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J220" s="12" t="inlineStr">
+        <is>
+          <t>Orden_Trabajo_Validacion con uuid y firma en Archivo.</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="41.4" customHeight="1" s="19">
       <c r="A221" s="11" t="inlineStr">
@@ -12819,16 +13293,22 @@
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H221" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I221" s="11" t="n"/>
-      <c r="J221" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I221" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J221" s="12" t="inlineStr">
+        <is>
+          <t>API_INS_ORDEN_TRABAJO_VALIDACION idempotente por uuid; resultado ACEPTADA/RECHAZADA validado en el SP.</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="55.2" customHeight="1" s="19">
       <c r="A222" s="11" t="inlineStr">
@@ -12866,11 +13346,17 @@
       </c>
       <c r="H222" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I222" s="11" t="n"/>
-      <c r="J222" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I222" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J222" s="12" t="inlineStr">
+        <is>
+          <t>GET /ordenes-trabajo/{id}/validaciones y /tipos-validacion.</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="41.4" customHeight="1" s="19">
       <c r="A223" s="11" t="inlineStr">
@@ -12903,16 +13389,22 @@
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H223" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I223" s="11" t="n"/>
-      <c r="J223" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I223" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J223" s="12" t="inlineStr">
+        <is>
+          <t>Append-only: un rechazo se supera con una validación posterior, ambas quedan.</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="41.4" customHeight="1" s="19">
       <c r="A224" s="11" t="inlineStr">
@@ -12945,16 +13437,22 @@
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H224" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I224" s="11" t="n"/>
-      <c r="J224" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I224" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J224" s="12" t="inlineStr">
+        <is>
+          <t>OT-29: RECHAZADA y luego ACEPTADA por Rodrigo.</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="27.6" customHeight="1" s="19">
       <c r="A225" s="11" t="inlineStr">
@@ -12992,11 +13490,17 @@
       </c>
       <c r="H225" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I225" s="11" t="n"/>
-      <c r="J225" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I225" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J225" s="12" t="inlineStr">
+        <is>
+          <t>POST /ordenes-trabajo/{id}/validaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="41.4" customHeight="1" s="19">
       <c r="A226" s="11" t="inlineStr">
@@ -13029,16 +13533,22 @@
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H226" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I226" s="11" t="n"/>
-      <c r="J226" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I226" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J226" s="12" t="inlineStr">
+        <is>
+          <t>Cubierto.</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="27.6" customHeight="1" s="19">
       <c r="A227" s="11" t="inlineStr">
@@ -13076,11 +13586,17 @@
       </c>
       <c r="H227" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I227" s="11" t="n"/>
-      <c r="J227" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I227" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J227" s="12" t="inlineStr">
+        <is>
+          <t>ValidacionAltaDto (tipo, resultado, observación, firma_base64).</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="41.4" customHeight="1" s="19">
       <c r="A228" s="11" t="inlineStr">
@@ -13113,7 +13629,7 @@
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H228" s="11" t="inlineStr">
@@ -13122,7 +13638,11 @@
         </is>
       </c>
       <c r="I228" s="11" t="n"/>
-      <c r="J228" s="12" t="n"/>
+      <c r="J228" s="12" t="inlineStr">
+        <is>
+          <t>Sin pantalla web propia en este bloque: las firmas se registran desde la app (hoja_firma) y se ven en la ficha web como validaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="27.6" customHeight="1" s="19">
       <c r="A229" s="11" t="inlineStr">
@@ -13164,7 +13684,11 @@
         </is>
       </c>
       <c r="I229" s="11" t="n"/>
-      <c r="J229" s="12" t="n"/>
+      <c r="J229" s="12" t="inlineStr">
+        <is>
+          <t>Idem T-5244.</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="27.6" customHeight="1" s="19">
       <c r="A230" s="11" t="inlineStr">
@@ -13197,16 +13721,22 @@
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H230" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I230" s="11" t="n"/>
-      <c r="J230" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I230" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J230" s="12" t="inlineStr">
+        <is>
+          <t>hoja_firma.dart + BloqueFirmas en la ficha de la OT.</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="27.6" customHeight="1" s="19">
       <c r="A231" s="11" t="inlineStr">
@@ -13244,11 +13774,17 @@
       </c>
       <c r="H231" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I231" s="11" t="n"/>
-      <c r="J231" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I231" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J231" s="12" t="inlineStr">
+        <is>
+          <t>VALIDAR ORDEN TRABAJO.</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="41.4" customHeight="1" s="19">
       <c r="A232" s="11" t="inlineStr">
@@ -13281,16 +13817,22 @@
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H232" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I232" s="11" t="n"/>
-      <c r="J232" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I232" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J232" s="12" t="inlineStr">
+        <is>
+          <t>#1 firma con tipo, resultado, fecha y usuario · #2 rechazo y validación posterior, ambas en el historial · #3 estado derivado al consultar (VALIDADA la calcula el SEL).</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="27.6" customHeight="1" s="19">
       <c r="A233" s="11" t="inlineStr">
@@ -13323,16 +13865,22 @@
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H233" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I233" s="11" t="n"/>
-      <c r="J233" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I233" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J233" s="12" t="inlineStr">
+        <is>
+          <t>MD 10.11.</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="27.6" customHeight="1" s="19">
       <c r="A234" s="11" t="inlineStr">
@@ -17194,7 +17742,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17227,7 +17775,7 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17806,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17290,7 +17838,7 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17676,7 +18224,7 @@
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17739,7 +18287,7 @@
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17899,7 +18447,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17933,7 +18481,7 @@
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17966,7 +18514,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17998,7 +18546,7 @@
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18061,7 +18609,7 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18642,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18125,7 +18673,7 @@
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18156,7 +18704,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18252,7 +18800,7 @@
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18315,7 +18863,7 @@
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -19012,7 +19560,7 @@
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -19044,7 +19592,7 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19624,7 @@
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
@@ -1430,7 +1430,7 @@
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O7" s="14" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="P7" s="14" t="inlineStr">
         <is>
-          <t>A nombre de Bryan (14-09-2026). Ya estaba construida; hoy la regla de obligatorios pasó al SP (BD/227). Pendiente validación de la PO.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. A nombre de Bryan (14-09-2026). Ya estaba construida; hoy la regla de obligatorios pasó al SP (BD/227). Pendiente validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -1505,11 +1505,15 @@
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="69" customHeight="1" s="19">
       <c r="A9" s="13" t="inlineStr">
@@ -1722,7 +1726,7 @@
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
@@ -1732,7 +1736,7 @@
       </c>
       <c r="P11" s="14" t="inlineStr">
         <is>
-          <t>A nombre de Bryan (14-09-2026). Ya estaba construida; verificada por HTTP hoy.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. A nombre de Bryan (14-09-2026). Ya estaba construida; verificada por HTTP hoy.</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1876,7 @@
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
@@ -1882,7 +1886,7 @@
       </c>
       <c r="P13" s="14" t="inlineStr">
         <is>
-          <t>A nombre de Bryan (14-09-2026). Ya estaba construida en la app; verificada por HTTP hoy (probar_ot_app.py). Pendiente validación de la PO.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. A nombre de Bryan (14-09-2026). Ya estaba construida en la app; verificada por HTTP hoy (probar_ot_app.py). Pendiente validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1951,7 @@
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr">
@@ -1957,7 +1961,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>A nombre de Bryan (14-09-2026). Ya estaba construida; hoy se destrabó el consumo del técnico (ubicaciones de bodega).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. A nombre de Bryan (14-09-2026). Ya estaba construida; hoy se destrabó el consumo del técnico (ubicaciones de bodega).</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2026,7 @@
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">
@@ -2032,7 +2036,7 @@
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>A nombre de Bryan (14-09-2026). BD/227: obligatorios pendientes rechazados con nombres, resultado y fecha fin real, advertencia sin mano de obra.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. A nombre de Bryan (14-09-2026). BD/227: obligatorios pendientes rechazados con nombres, resultado y fecha fin real, advertencia sin mano de obra.</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2176,7 @@
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
@@ -2182,7 +2186,7 @@
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>A nombre de Bryan (14-09-2026). Ya estaba construida; hoy el ejecutante inválido se rechaza con mensaje (BD/227).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. A nombre de Bryan (14-09-2026). Ya estaba construida; hoy el ejecutante inválido se rechaza con mensaje (BD/227).</t>
         </is>
       </c>
     </row>
@@ -2464,13 +2468,13 @@
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O21" s="14" t="n"/>
       <c r="P21" s="14" t="inlineStr">
         <is>
-          <t>· ALCANCE APP (30-08): App y Web → App. Solo App (R3): el tecnico escribe. Comentar y rectificar es HU-131.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el tecnico escribe. Comentar y rectificar es HU-131.</t>
         </is>
       </c>
     </row>
@@ -2535,11 +2539,15 @@
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="69" customHeight="1" s="19">
       <c r="A23" s="13" t="inlineStr">
@@ -2602,11 +2610,15 @@
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O23" s="14" t="n"/>
-      <c r="P23" s="14" t="n"/>
+      <c r="P23" s="14" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="82.90000000000001" customHeight="1" s="19">
       <c r="A24" s="11" t="inlineStr">
@@ -2878,11 +2890,15 @@
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O27" s="14" t="n"/>
-      <c r="P27" s="14" t="n"/>
+      <c r="P27" s="14" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="82.90000000000001" customHeight="1" s="19">
       <c r="A28" s="11" t="inlineStr">
@@ -2945,11 +2961,15 @@
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
+      <c r="P28" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55.15" customHeight="1" s="19">
       <c r="A29" s="13" t="inlineStr">
@@ -3830,7 +3850,7 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I16" s="11" t="n">
@@ -3838,7 +3858,7 @@
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>Ya existía (nueva_orden_screen, encolada con uuid). Hoy además la correctiva nace desde la ficha de la falla (POST /fallas/{id}/orden).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existía (nueva_orden_screen, encolada con uuid). Hoy además la correctiva nace desde la ficha de la falla (POST /fallas/{id}/orden).</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4090,7 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I21" s="11" t="n">
@@ -4078,7 +4098,7 @@
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>Orden_Trabajo_Paso: otp_obligatorio, otp_resultado_paso (4 PENDIENTE), otp_uuid con UQ_OTP_UUID (BD/209).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Orden_Trabajo_Paso: otp_obligatorio, otp_resultado_paso (4 PENDIENTE), otp_uuid con UQ_OTP_UUID (BD/209).</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4138,7 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I22" s="11" t="n">
@@ -4126,7 +4146,7 @@
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>Los pasos viajan dentro de GET /ordenes-trabajo/{id} (API_SEL_ORDEN_TRABAJO_PASO), acotados al cliente y las plantas del usuario.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Los pasos viajan dentro de GET /ordenes-trabajo/{id} (API_SEL_ORDEN_TRABAJO_PASO), acotados al cliente y las plantas del usuario.</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4186,7 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I23" s="11" t="n">
@@ -4174,7 +4194,7 @@
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>API_INS_ORDEN_TRABAJO_PASO idempotente por uuid (BD/209); el resultado de un paso por API_UPD_ORDEN_TRABAJO_PASO.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. API_INS_ORDEN_TRABAJO_PASO idempotente por uuid (BD/209); el resultado de un paso por API_UPD_ORDEN_TRABAJO_PASO.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4234,7 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I24" s="11" t="n">
@@ -4222,7 +4242,7 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>OT-27..32 creadas desde la app con dos pasos obligatorios cada una.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. OT-27..32 creadas desde la app con dos pasos obligatorios cada una.</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4282,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I25" s="11" t="n">
@@ -4270,7 +4290,7 @@
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>Sin endpoint /sync aparte: la ficha completa baja en un viaje y la sábana (bloque ORDENES_TRABAJO) cubre el offline.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Sin endpoint /sync aparte: la ficha completa baja en un viaje y la sábana (bloque ORDENES_TRABAJO) cubre el offline.</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4330,7 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I26" s="11" t="n">
@@ -4318,7 +4338,7 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>POST /ordenes-trabajo/pasos/{id} y POST /ordenes-trabajo/{id}/pasos, idempotentes por uuid, salen de la cola (outbox) uno a uno.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. POST /ordenes-trabajo/pasos/{id} y POST /ordenes-trabajo/{id}/pasos, idempotentes por uuid, salen de la cola (outbox) uno a uno.</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4378,7 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I27" s="11" t="n">
@@ -4366,7 +4386,7 @@
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>Ya existía: FNC_SUSCRIPCION_VIGENTE → 402 en ApiBase.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existía: FNC_SUSCRIPCION_VIGENTE → 402 en ApiBase.</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4426,7 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I28" s="11" t="n">
@@ -4414,7 +4434,7 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>orden_ficha_screen + hoja_paso: pestaña Pasos con objetivos grandes, conforme / no conforme / no aplica con comentario.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. orden_ficha_screen + hoja_paso: pestaña Pasos con objetivos grandes, conforme / no conforme / no aplica con comentario.</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4474,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I29" s="11" t="n">
@@ -4462,7 +4482,7 @@
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>OutboxService: SQLite primero, uuid al encolar; PASO en la cola.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. OutboxService: SQLite primero, uuid al encolar; PASO en la cola.</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4522,7 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I30" s="11" t="n">
@@ -4510,7 +4530,7 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>Reintento con el mismo uuid → misma respuesta (probado: reintento del alta devuelve el mismo id).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Reintento con el mismo uuid → misma respuesta (probado: reintento del alta devuelve el mismo id).</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4570,7 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I31" s="11" t="n">
@@ -4558,7 +4578,7 @@
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>EJECUTAR ORDEN TRABAJO en el endpoint; el SP exige estar asignado y la OT en ejecución.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. EJECUTAR ORDEN TRABAJO en el endpoint; el SP exige estar asignado y la OT en ejecución.</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4618,7 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I32" s="11" t="n">
@@ -4606,7 +4626,7 @@
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>#1 conforme con ejecutor y hora · #2 no aplica con comentario · #3 obligatorio pendiente: ahora lo rechaza el SP y nombra los pasos (BD/227) · #4 medición: queda en la serie del activo vía /captura/mediciones (HU-043) · #5 offline: cola verificada en sesiones anteriores.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. #1 conforme con ejecutor y hora · #2 no aplica con comentario · #3 obligatorio pendiente: ahora lo rechaza el SP y nombra los pasos (BD/227) · #4 medición: queda en la serie del activo vía /captura/mediciones (HU-043) · #5 offline: cola verificada en sesiones anteriores.</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4666,7 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I33" s="11" t="n">
@@ -4654,7 +4674,7 @@
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>XML en OrdenesTrabajoController; MD 10.11.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. XML en OrdenesTrabajoController; MD 10.11.</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4714,7 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I34" s="11" t="n">
@@ -4702,7 +4722,7 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>Pendiente de la PO; historia En revisión.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Pendiente de la PO; historia En revisión.</t>
         </is>
       </c>
     </row>
@@ -4742,11 +4762,15 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I35" s="11" t="n"/>
-      <c r="J35" s="12" t="n"/>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="41.45" customHeight="1" s="19">
       <c r="A36" s="11" t="inlineStr">
@@ -4784,11 +4808,15 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I36" s="11" t="n"/>
-      <c r="J36" s="12" t="n"/>
+      <c r="J36" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="27.6" customHeight="1" s="19">
       <c r="A37" s="11" t="inlineStr">
@@ -4826,11 +4854,15 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I37" s="11" t="n"/>
-      <c r="J37" s="12" t="n"/>
+      <c r="J37" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="41.45" customHeight="1" s="19">
       <c r="A38" s="11" t="inlineStr">
@@ -4868,11 +4900,15 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I38" s="11" t="n"/>
-      <c r="J38" s="12" t="n"/>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="27.6" customHeight="1" s="19">
       <c r="A39" s="11" t="inlineStr">
@@ -4910,11 +4946,15 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I39" s="11" t="n"/>
-      <c r="J39" s="12" t="n"/>
+      <c r="J39" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="27.6" customHeight="1" s="19">
       <c r="A40" s="11" t="inlineStr">
@@ -4952,11 +4992,15 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I40" s="11" t="n"/>
-      <c r="J40" s="12" t="n"/>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="27.6" customHeight="1" s="19">
       <c r="A41" s="11" t="inlineStr">
@@ -4994,11 +5038,15 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I41" s="11" t="n"/>
-      <c r="J41" s="12" t="n"/>
+      <c r="J41" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="41.45" customHeight="1" s="19">
       <c r="A42" s="11" t="inlineStr">
@@ -5036,11 +5084,15 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I42" s="11" t="n"/>
-      <c r="J42" s="12" t="n"/>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="27.6" customHeight="1" s="19">
       <c r="A43" s="11" t="inlineStr">
@@ -5078,11 +5130,15 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I43" s="11" t="n"/>
-      <c r="J43" s="12" t="n"/>
+      <c r="J43" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="27.6" customHeight="1" s="19">
       <c r="A44" s="11" t="inlineStr">
@@ -5120,11 +5176,15 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I44" s="11" t="n"/>
-      <c r="J44" s="12" t="n"/>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="27.6" customHeight="1" s="19">
       <c r="A45" s="11" t="inlineStr">
@@ -5162,11 +5222,15 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I45" s="11" t="n"/>
-      <c r="J45" s="12" t="n"/>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="27.6" customHeight="1" s="19">
       <c r="A46" s="11" t="inlineStr">
@@ -5204,11 +5268,15 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I46" s="11" t="n"/>
-      <c r="J46" s="12" t="n"/>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="55.15" customHeight="1" s="19">
       <c r="A47" s="11" t="inlineStr">
@@ -5246,11 +5314,15 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I47" s="11" t="n"/>
-      <c r="J47" s="12" t="n"/>
+      <c r="J47" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="41.45" customHeight="1" s="19">
       <c r="A48" s="11" t="inlineStr">
@@ -5288,11 +5360,15 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I48" s="11" t="n"/>
-      <c r="J48" s="12" t="n"/>
+      <c r="J48" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="41.45" customHeight="1" s="19">
       <c r="A49" s="11" t="inlineStr">
@@ -6194,7 +6270,7 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I67" s="11" t="n">
@@ -6202,7 +6278,7 @@
       </c>
       <c r="J67" s="12" t="inlineStr">
         <is>
-          <t>Índices por cliente+estado existentes.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Índices por cliente+estado existentes.</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6318,7 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I68" s="11" t="n">
@@ -6250,7 +6326,7 @@
       </c>
       <c r="J68" s="12" t="inlineStr">
         <is>
-          <t>API_SEL_ORDEN_TRABAJO_BANDEJA con @AMBITO 1/2/3, SITUACION (VENCIDA / VENCE HOY / EN PLAZO) calculada en el SP.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. API_SEL_ORDEN_TRABAJO_BANDEJA con @AMBITO 1/2/3, SITUACION (VENCIDA / VENCE HOY / EN PLAZO) calculada en el SP.</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6366,7 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I69" s="11" t="n">
@@ -6298,7 +6374,7 @@
       </c>
       <c r="J69" s="12" t="inlineStr">
         <is>
-          <t>Cubierto por los índices existentes.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Cubierto por los índices existentes.</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6414,7 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I70" s="11" t="n">
@@ -6346,7 +6422,7 @@
       </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>OT-27..32 de prueba; bandeja de Cristián con 5 y disponibles 10.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. OT-27..32 de prueba; bandeja de Cristián con 5 y disponibles 10.</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6462,7 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I71" s="11" t="n">
@@ -6394,7 +6470,7 @@
       </c>
       <c r="J71" s="12" t="inlineStr">
         <is>
-          <t>GET /ordenes-trabajo?ambito=&amp;instalacion=&amp;desde= (paginado en el SP).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. GET /ordenes-trabajo?ambito=&amp;instalacion=&amp;desde= (paginado en el SP).</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6510,7 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I72" s="11" t="n">
@@ -6442,7 +6518,7 @@
       </c>
       <c r="J72" s="12" t="inlineStr">
         <is>
-          <t>No hay caché en servidor: la app guarda la última bandeja en SQLite (sábana) y la muestra sin señal, que es lo que pide el criterio 2.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. No hay caché en servidor: la app guarda la última bandeja en SQLite (sábana) y la muestra sin señal, que es lo que pide el criterio 2.</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6558,7 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I73" s="11" t="n">
@@ -6490,7 +6566,7 @@
       </c>
       <c r="J73" s="12" t="inlineStr">
         <is>
-          <t>ordenes_screen.dart: pestañas Mías / Disponibles / Planta; mi_trabajo_screen une órdenes, tareas y pautas.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. ordenes_screen.dart: pestañas Mías / Disponibles / Planta; mi_trabajo_screen une órdenes, tareas y pautas.</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6606,7 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I74" s="11" t="n">
@@ -6538,7 +6614,7 @@
       </c>
       <c r="J74" s="12" t="inlineStr">
         <is>
-          <t>VER ORDENES TRABAJO; el SP filtra por cliente y plantas del usuario.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. VER ORDENES TRABAJO; el SP filtra por cliente y plantas del usuario.</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6654,7 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I75" s="11" t="n">
@@ -6586,7 +6662,7 @@
       </c>
       <c r="J75" s="12" t="inlineStr">
         <is>
-          <t>#1 bandeja con SITUACION (HTTP) · #2 sin conexión desde la sábana (verificado en sesiones anteriores, bloque ORDENES_TRABAJO) · #3 disponibles: la OT nueva aparece sin dueño (HTTP).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. #1 bandeja con SITUACION (HTTP) · #2 sin conexión desde la sábana (verificado en sesiones anteriores, bloque ORDENES_TRABAJO) · #3 disponibles: la OT nueva aparece sin dueño (HTTP).</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6702,7 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I76" s="11" t="n">
@@ -6634,7 +6710,7 @@
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
-          <t>MD 10.11.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. MD 10.11.</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7278,7 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I88" s="11" t="n">
@@ -7210,7 +7286,7 @@
       </c>
       <c r="J88" s="12" t="inlineStr">
         <is>
-          <t>hoja_asignar.dart: responsable o apoyo desde la ficha de la OT, con la gente de la planta; encolada con uuid (BD/226).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. hoja_asignar.dart: responsable o apoyo desde la ficha de la OT, con la gente de la planta; encolada con uuid (BD/226).</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7326,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I89" s="11" t="n">
@@ -7258,7 +7334,7 @@
       </c>
       <c r="J89" s="12" t="inlineStr">
         <is>
-          <t>Orden_Trabajo_Asignacion con UX_OTA_RESPONSABLE filtrado.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Orden_Trabajo_Asignacion con UX_OTA_RESPONSABLE filtrado.</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7374,7 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I90" s="11" t="n">
@@ -7306,7 +7382,7 @@
       </c>
       <c r="J90" s="12" t="inlineStr">
         <is>
-          <t>API_UPD_ORDEN_TRABAJO_TOMAR: UPDATE … WHERE estado = 1 con @@ROWCOUNT (la carrera se resuelve en la base).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. API_UPD_ORDEN_TRABAJO_TOMAR: UPDATE … WHERE estado = 1 con @@ROWCOUNT (la carrera se resuelve en la base).</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7422,7 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I91" s="11" t="n">
@@ -7354,7 +7430,7 @@
       </c>
       <c r="J91" s="12" t="inlineStr">
         <is>
-          <t>La regla vive en el SP; web y app reciben el mismo veredicto.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. La regla vive en el SP; web y app reciben el mismo veredicto.</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7470,7 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I92" s="11" t="n">
@@ -7402,7 +7478,7 @@
       </c>
       <c r="J92" s="12" t="inlineStr">
         <is>
-          <t>El resultado se lee en GET /ordenes-trabajo/{id} (estado y asignados).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. El resultado se lee en GET /ordenes-trabajo/{id} (estado y asignados).</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7518,7 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I93" s="11" t="n">
@@ -7450,7 +7526,7 @@
       </c>
       <c r="J93" s="12" t="inlineStr">
         <is>
-          <t>OT-29: Cristián toma, Paula llega segunda.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. OT-29: Cristián toma, Paula llega segunda.</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7566,7 @@
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I94" s="11" t="n">
@@ -7498,7 +7574,7 @@
       </c>
       <c r="J94" s="12" t="inlineStr">
         <is>
-          <t>POST /ordenes-trabajo/{id}/tomar.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. POST /ordenes-trabajo/{id}/tomar.</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7614,7 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I95" s="11" t="n">
@@ -7546,7 +7622,7 @@
       </c>
       <c r="J95" s="12" t="inlineStr">
         <is>
-          <t>«La orden ya fue tomada por otro usuario o no está abierta» llega como 400 de negocio con mensaje, no como 500.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. «La orden ya fue tomada por otro usuario o no está abierta» llega como 400 de negocio con mensaje, no como 500.</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7662,7 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I96" s="11" t="n">
@@ -7594,7 +7670,7 @@
       </c>
       <c r="J96" s="12" t="inlineStr">
         <is>
-          <t>Botón «Tomar trabajo» en la ficha; arranca el cronómetro.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Botón «Tomar trabajo» en la ficha; arranca el cronómetro.</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7710,7 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I97" s="11" t="n">
@@ -7642,7 +7718,7 @@
       </c>
       <c r="J97" s="12" t="inlineStr">
         <is>
-          <t>TOMAR ORDEN TRABAJO en el endpoint.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. TOMAR ORDEN TRABAJO en el endpoint.</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7758,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I98" s="11" t="n">
@@ -7690,7 +7766,7 @@
       </c>
       <c r="J98" s="12" t="inlineStr">
         <is>
-          <t>#1 toma → EN EJECUCION y responsable · #2 dos técnicos: el segundo recibe «ya fue tomada» · #3 sumar compañero: dos asignados, un responsable (POST asignaciones con es_responsable=false).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. #1 toma → EN EJECUCION y responsable · #2 dos técnicos: el segundo recibe «ya fue tomada» · #3 sumar compañero: dos asignados, un responsable (POST asignaciones con es_responsable=false).</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7806,7 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I99" s="11" t="n">
@@ -7738,7 +7814,7 @@
       </c>
       <c r="J99" s="12" t="inlineStr">
         <is>
-          <t>MD 10.11.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. MD 10.11.</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7854,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I100" s="11" t="n">
@@ -7786,7 +7862,7 @@
       </c>
       <c r="J100" s="12" t="inlineStr">
         <is>
-          <t>Orden_Trabajo_Repuesto: consumida / devuelta / costo unitario; uuid del movimiento.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Orden_Trabajo_Repuesto: consumida / devuelta / costo unitario; uuid del movimiento.</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7902,7 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I101" s="11" t="n">
@@ -7834,7 +7910,7 @@
       </c>
       <c r="J101" s="12" t="inlineStr">
         <is>
-          <t>API_INS_ORDEN_TRABAJO_REPUESTO mueve inventario y orden en una transacción; exige ubicación si la bodega las tiene.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. API_INS_ORDEN_TRABAJO_REPUESTO mueve inventario y orden en una transacción; exige ubicación si la bodega las tiene.</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7950,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I102" s="11" t="n">
@@ -7882,7 +7958,7 @@
       </c>
       <c r="J102" s="12" t="inlineStr">
         <is>
-          <t>GET /ordenes-trabajo/{id}/recursos (repuestos con consumido y devuelto) y /repuestos-disponibles con ES_COMPATIBLE.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. GET /ordenes-trabajo/{id}/recursos (repuestos con consumido y devuelto) y /repuestos-disponibles con ES_COMPATIBLE.</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7998,7 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I103" s="11" t="n">
@@ -7930,7 +8006,7 @@
       </c>
       <c r="J103" s="12" t="inlineStr">
         <is>
-          <t>No hay UPD: consumo y devolución son movimientos (append), la corrección es una devolución.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. No hay UPD: consumo y devolución son movimientos (append), la corrección es una devolución.</t>
         </is>
       </c>
     </row>
@@ -7970,7 +8046,7 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I104" s="11" t="n">
@@ -7978,7 +8054,7 @@
       </c>
       <c r="J104" s="12" t="inlineStr">
         <is>
-          <t>REP-6205 en Bodega Frío: consumido 1 y devuelto 1 sobre OT-31.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. REP-6205 en Bodega Frío: consumido 1 y devuelto 1 sobre OT-31.</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8094,7 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I105" s="11" t="n">
@@ -8026,7 +8102,7 @@
       </c>
       <c r="J105" s="12" t="inlineStr">
         <is>
-          <t>POST /ordenes-trabajo/{id}/repuestos idempotente por uuid (reintento no consume dos veces).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. POST /ordenes-trabajo/{id}/repuestos idempotente por uuid (reintento no consume dos veces).</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8142,7 @@
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I106" s="11" t="n">
@@ -8074,7 +8150,7 @@
       </c>
       <c r="J106" s="12" t="inlineStr">
         <is>
-          <t>Cubierto por /recursos y /repuestos-disponibles.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Cubierto por /recursos y /repuestos-disponibles.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8190,7 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I107" s="11" t="n">
@@ -8122,7 +8198,7 @@
       </c>
       <c r="J107" s="12" t="inlineStr">
         <is>
-          <t>OrdenTrabajoRepuestoAltaDto; ExigirCuerpo.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. OrdenTrabajoRepuestoAltaDto; ExigirCuerpo.</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8238,7 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I108" s="11" t="n">
@@ -8170,7 +8246,7 @@
       </c>
       <c r="J108" s="12" t="inlineStr">
         <is>
-          <t>hojas_recursos.dart: consumo y devolución con bodega y estante. Defecto corregido hoy: GET /bodegas/{id}/ubicaciones daba 403 al técnico (VER BODEGAS) y dejaba el consumo sin camino; ahora acepta EJECUTAR ORDEN TRABAJO.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. hojas_recursos.dart: consumo y devolución con bodega y estante. Defecto corregido hoy: GET /bodegas/{id}/ubicaciones daba 403 al técnico (VER BODEGAS) y dejaba el consumo sin camino; ahora acepta EJECUTAR ORDEN TRABAJO.</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8286,7 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I109" s="11" t="n">
@@ -8218,7 +8294,7 @@
       </c>
       <c r="J109" s="12" t="inlineStr">
         <is>
-          <t>EJECUTAR ORDEN TRABAJO; cliente del token.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. EJECUTAR ORDEN TRABAJO; cliente del token.</t>
         </is>
       </c>
     </row>
@@ -8258,7 +8334,7 @@
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I110" s="11" t="n">
@@ -8266,7 +8342,7 @@
       </c>
       <c r="J110" s="12" t="inlineStr">
         <is>
-          <t>#1 consumo descuenta y suma costo (SP en transacción) · #2 horómetro de la pieza: campos opcionales del DTO (no verificado con datos) · #3 devolución: consumido 0, devuelto 1.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. #1 consumo descuenta y suma costo (SP en transacción) · #2 horómetro de la pieza: campos opcionales del DTO (no verificado con datos) · #3 devolución: consumido 0, devuelto 1.</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8382,7 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I111" s="11" t="n">
@@ -8314,7 +8390,7 @@
       </c>
       <c r="J111" s="12" t="inlineStr">
         <is>
-          <t>MD 10.11.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. MD 10.11.</t>
         </is>
       </c>
     </row>
@@ -8354,7 +8430,7 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I112" s="11" t="n">
@@ -8362,7 +8438,7 @@
       </c>
       <c r="J112" s="12" t="inlineStr">
         <is>
-          <t>otr_resultado, otr_fecha_fin_real_utc, otr_duracion_real_minuto.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. otr_resultado, otr_fecha_fin_real_utc, otr_duracion_real_minuto.</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8478,7 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I113" s="11" t="n">
@@ -8410,7 +8486,7 @@
       </c>
       <c r="J113" s="12" t="inlineStr">
         <is>
-          <t>BD/227 UPD_ORDEN_TRABAJO_FINALIZAR: rechaza con los nombres de los obligatorios pendientes, guarda resultado y fecha fin real, advierte sin mano de obra.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. BD/227 UPD_ORDEN_TRABAJO_FINALIZAR: rechaza con los nombres de los obligatorios pendientes, guarda resultado y fecha fin real, advierte sin mano de obra.</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8526,7 @@
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I114" s="11" t="n">
@@ -8458,7 +8534,7 @@
       </c>
       <c r="J114" s="12" t="inlineStr">
         <is>
-          <t>La regla pasó del botón de la app al SP: probado por HTTP que antes el endpoint dejaba finalizar con obligatorios pendientes.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. La regla pasó del botón de la app al SP: probado por HTTP que antes el endpoint dejaba finalizar con obligatorios pendientes.</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8574,7 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I115" s="11" t="n">
@@ -8506,7 +8582,7 @@
       </c>
       <c r="J115" s="12" t="inlineStr">
         <is>
-          <t>El SP devuelve ORDEN_TRABAJO, ESTADO, ADVERTENCIA; la API la expone como `advertencia`.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. El SP devuelve ORDEN_TRABAJO, ESTADO, ADVERTENCIA; la API la expone como `advertencia`.</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8622,7 @@
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I116" s="11" t="n">
@@ -8554,7 +8630,7 @@
       </c>
       <c r="J116" s="12" t="inlineStr">
         <is>
-          <t>OT-29..32.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. OT-29..32.</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8670,7 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I117" s="11" t="n">
@@ -8602,7 +8678,7 @@
       </c>
       <c r="J117" s="12" t="inlineStr">
         <is>
-          <t>POST /ordenes-trabajo/{id}/finalizar → 200 {otr_id, advertencia}.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. POST /ordenes-trabajo/{id}/finalizar → 200 {otr_id, advertencia}.</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8718,7 @@
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I118" s="11" t="n">
@@ -8650,7 +8726,7 @@
       </c>
       <c r="J118" s="12" t="inlineStr">
         <is>
-          <t>«Faltan pasos obligatorios por resolver: Revisar rodamiento, Medir vibración» → 400 con mensaje.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. «Faltan pasos obligatorios por resolver: Revisar rodamiento, Medir vibración» → 400 con mensaje.</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8766,7 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I119" s="11" t="n">
@@ -8698,7 +8774,7 @@
       </c>
       <c r="J119" s="12" t="inlineStr">
         <is>
-          <t>orden_ficha_screen: diálogo de resultado, tiempo del cronómetro como mano de obra, y la advertencia del servidor en pantalla.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. orden_ficha_screen: diálogo de resultado, tiempo del cronómetro como mano de obra, y la advertencia del servidor en pantalla.</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8814,7 @@
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I120" s="11" t="n">
@@ -8746,7 +8822,7 @@
       </c>
       <c r="J120" s="12" t="inlineStr">
         <is>
-          <t>EJECUTAR ORDEN TRABAJO.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. EJECUTAR ORDEN TRABAJO.</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8862,7 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I121" s="11" t="n">
@@ -8794,7 +8870,7 @@
       </c>
       <c r="J121" s="12" t="inlineStr">
         <is>
-          <t>#1 finaliza → EN ESPERA DE CIERRE y no se modifica (paso rechazado) · #2 obligatorios pendientes → 400 con nombres · #3 sin mano de obra → advertencia y se permite (SP).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. #1 finaliza → EN ESPERA DE CIERRE y no se modifica (paso rechazado) · #2 obligatorios pendientes → 400 con nombres · #3 sin mano de obra → advertencia y se permite (SP).</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8910,7 @@
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I122" s="11" t="n">
@@ -8842,7 +8918,7 @@
       </c>
       <c r="J122" s="12" t="inlineStr">
         <is>
-          <t>MD 10.11.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. MD 10.11.</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9342,7 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I131" s="11" t="n">
@@ -9274,7 +9350,7 @@
       </c>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>Orden_Trabajo_Mano_Obra: usuario o proveedor, minutos, costo hora y moneda, uuid.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Orden_Trabajo_Mano_Obra: usuario o proveedor, minutos, costo hora y moneda, uuid.</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9390,7 @@
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I132" s="11" t="n">
@@ -9322,7 +9398,7 @@
       </c>
       <c r="J132" s="12" t="inlineStr">
         <is>
-          <t>API_INS_ORDEN_TRABAJO_MANO_OBRA (BD/193) + BD/227: el ejecutante se valida antes de insertar.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. API_INS_ORDEN_TRABAJO_MANO_OBRA (BD/193) + BD/227: el ejecutante se valida antes de insertar.</t>
         </is>
       </c>
     </row>
@@ -9362,7 +9438,7 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I133" s="11" t="n">
@@ -9370,7 +9446,7 @@
       </c>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>GET /ordenes-trabajo/{id}/recursos.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. GET /ordenes-trabajo/{id}/recursos.</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9486,7 @@
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I134" s="11" t="n">
@@ -9418,7 +9494,7 @@
       </c>
       <c r="J134" s="12" t="inlineStr">
         <is>
-          <t>Append-only: no hay UPD, se corrige agregando otro tramo.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Append-only: no hay UPD, se corrige agregando otro tramo.</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9534,7 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I135" s="11" t="n">
@@ -9466,7 +9542,7 @@
       </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>Tramo de 90 min sobre OT-29..32.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Tramo de 90 min sobre OT-29..32.</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9582,7 @@
       </c>
       <c r="H136" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I136" s="11" t="n">
@@ -9514,7 +9590,7 @@
       </c>
       <c r="J136" s="12" t="inlineStr">
         <is>
-          <t>POST /ordenes-trabajo/{id}/mano-obra idempotente por uuid.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. POST /ordenes-trabajo/{id}/mano-obra idempotente por uuid.</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9630,7 @@
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I137" s="11" t="n">
@@ -9562,7 +9638,7 @@
       </c>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>Cubierto por /recursos.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Cubierto por /recursos.</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9678,7 @@
       </c>
       <c r="H138" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I138" s="11" t="n">
@@ -9610,7 +9686,7 @@
       </c>
       <c r="J138" s="12" t="inlineStr">
         <is>
-          <t>ManoObraAltaDto.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. ManoObraAltaDto.</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9726,7 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I139" s="11" t="n">
@@ -9658,7 +9734,7 @@
       </c>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>hojas_recursos.dart (tramo manual) y cronómetro que se anota al finalizar.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. hojas_recursos.dart (tramo manual) y cronómetro que se anota al finalizar.</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9774,7 @@
       </c>
       <c r="H140" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I140" s="11" t="n">
@@ -9706,7 +9782,7 @@
       </c>
       <c r="J140" s="12" t="inlineStr">
         <is>
-          <t>EJECUTAR ORDEN TRABAJO; plantas del usuario.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. EJECUTAR ORDEN TRABAJO; plantas del usuario.</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9822,7 @@
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I141" s="11" t="n">
@@ -9754,7 +9830,7 @@
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>#1 minutos calculados = 90 y duración real = suma · #2 externa: proveedor y valor hora en el modelo (no verificado con datos de proveedor) · #3 sin ejecutante válido → rechazado con mensaje (antes FK cruda).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. #1 minutos calculados = 90 y duración real = suma · #2 externa: proveedor y valor hora en el modelo (no verificado con datos de proveedor) · #3 sin ejecutante válido → rechazado con mensaje (antes FK cruda).</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9870,7 @@
       </c>
       <c r="H142" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I142" s="11" t="n">
@@ -9802,7 +9878,7 @@
       </c>
       <c r="J142" s="12" t="inlineStr">
         <is>
-          <t>MD 10.11.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. MD 10.11.</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10818,7 @@
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I163" s="11" t="n">
@@ -10750,7 +10826,7 @@
       </c>
       <c r="J163" s="12" t="inlineStr">
         <is>
-          <t>fallas_screen / nueva_falla_screen / falla_ficha_screen: registrar, diagnósticos, acciones, parada y abrir la correctiva; menú app://fallas; todo encolado con uuid (BD/226).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. fallas_screen / nueva_falla_screen / falla_ficha_screen: registrar, diagnósticos, acciones, parada y abrir la correctiva; menú app://fallas; todo encolado con uuid (BD/226).</t>
         </is>
       </c>
     </row>
@@ -11462,7 +11538,7 @@
       </c>
       <c r="H178" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I178" s="11" t="n">
@@ -11470,7 +11546,7 @@
       </c>
       <c r="J178" s="12" t="inlineStr">
         <is>
-          <t>hoja_indisponibilidad.dart desde la OT y desde la falla; encolada con uuid (BD/226).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. hoja_indisponibilidad.dart desde la OT y desde la falla; encolada con uuid (BD/226).</t>
         </is>
       </c>
     </row>
@@ -11654,11 +11730,15 @@
       </c>
       <c r="H182" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I182" s="11" t="n"/>
-      <c r="J182" s="12" t="n"/>
+      <c r="J182" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="41.45" customHeight="1" s="19">
       <c r="A183" s="11" t="inlineStr">
@@ -11696,11 +11776,15 @@
       </c>
       <c r="H183" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I183" s="11" t="n"/>
-      <c r="J183" s="12" t="n"/>
+      <c r="J183" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="27.6" customHeight="1" s="19">
       <c r="A184" s="11" t="inlineStr">
@@ -11738,11 +11822,15 @@
       </c>
       <c r="H184" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I184" s="11" t="n"/>
-      <c r="J184" s="12" t="n"/>
+      <c r="J184" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="41.45" customHeight="1" s="19">
       <c r="A185" s="11" t="inlineStr">
@@ -11780,11 +11868,15 @@
       </c>
       <c r="H185" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I185" s="11" t="n"/>
-      <c r="J185" s="12" t="n"/>
+      <c r="J185" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="41.45" customHeight="1" s="19">
       <c r="A186" s="11" t="inlineStr">
@@ -11822,11 +11914,15 @@
       </c>
       <c r="H186" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I186" s="11" t="n"/>
-      <c r="J186" s="12" t="n"/>
+      <c r="J186" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="27.6" customHeight="1" s="19">
       <c r="A187" s="11" t="inlineStr">
@@ -11864,11 +11960,15 @@
       </c>
       <c r="H187" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I187" s="11" t="n"/>
-      <c r="J187" s="12" t="n"/>
+      <c r="J187" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="27.6" customHeight="1" s="19">
       <c r="A188" s="11" t="inlineStr">
@@ -11906,11 +12006,15 @@
       </c>
       <c r="H188" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I188" s="11" t="n"/>
-      <c r="J188" s="12" t="n"/>
+      <c r="J188" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="27.6" customHeight="1" s="19">
       <c r="A189" s="11" t="inlineStr">
@@ -11948,11 +12052,15 @@
       </c>
       <c r="H189" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I189" s="11" t="n"/>
-      <c r="J189" s="12" t="n"/>
+      <c r="J189" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="41.45" customHeight="1" s="19">
       <c r="A190" s="11" t="inlineStr">
@@ -11990,11 +12098,15 @@
       </c>
       <c r="H190" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I190" s="11" t="n"/>
-      <c r="J190" s="12" t="n"/>
+      <c r="J190" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="27.6" customHeight="1" s="19">
       <c r="A191" s="11" t="inlineStr">
@@ -12032,11 +12144,15 @@
       </c>
       <c r="H191" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I191" s="11" t="n"/>
-      <c r="J191" s="12" t="n"/>
+      <c r="J191" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="27.6" customHeight="1" s="19">
       <c r="A192" s="11" t="inlineStr">
@@ -12074,11 +12190,15 @@
       </c>
       <c r="H192" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I192" s="11" t="n"/>
-      <c r="J192" s="12" t="n"/>
+      <c r="J192" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="27.6" customHeight="1" s="19">
       <c r="A193" s="11" t="inlineStr">
@@ -12116,11 +12236,15 @@
       </c>
       <c r="H193" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I193" s="11" t="n"/>
-      <c r="J193" s="12" t="n"/>
+      <c r="J193" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="27.6" customHeight="1" s="19">
       <c r="A194" s="11" t="inlineStr">
@@ -12158,11 +12282,15 @@
       </c>
       <c r="H194" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I194" s="11" t="n"/>
-      <c r="J194" s="12" t="n"/>
+      <c r="J194" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="41.45" customHeight="1" s="19">
       <c r="A195" s="11" t="inlineStr">
@@ -12200,11 +12328,15 @@
       </c>
       <c r="H195" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I195" s="11" t="n"/>
-      <c r="J195" s="12" t="n"/>
+      <c r="J195" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="55.15" customHeight="1" s="19">
       <c r="A196" s="11" t="inlineStr">
@@ -12242,11 +12374,15 @@
       </c>
       <c r="H196" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I196" s="11" t="n"/>
-      <c r="J196" s="12" t="n"/>
+      <c r="J196" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="41.45" customHeight="1" s="19">
       <c r="A197" s="11" t="inlineStr">
@@ -12284,11 +12420,15 @@
       </c>
       <c r="H197" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I197" s="11" t="n"/>
-      <c r="J197" s="12" t="n"/>
+      <c r="J197" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="41.45" customHeight="1" s="19">
       <c r="A198" s="11" t="inlineStr">
@@ -12326,11 +12466,15 @@
       </c>
       <c r="H198" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I198" s="11" t="n"/>
-      <c r="J198" s="12" t="n"/>
+      <c r="J198" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="27.6" customHeight="1" s="19">
       <c r="A199" s="11" t="inlineStr">
@@ -12368,11 +12512,15 @@
       </c>
       <c r="H199" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I199" s="11" t="n"/>
-      <c r="J199" s="12" t="n"/>
+      <c r="J199" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="41.45" customHeight="1" s="19">
       <c r="A200" s="11" t="inlineStr">
@@ -12410,11 +12558,15 @@
       </c>
       <c r="H200" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I200" s="11" t="n"/>
-      <c r="J200" s="12" t="n"/>
+      <c r="J200" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="27.6" customHeight="1" s="19">
       <c r="A201" s="11" t="inlineStr">
@@ -12452,11 +12604,15 @@
       </c>
       <c r="H201" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I201" s="11" t="n"/>
-      <c r="J201" s="12" t="n"/>
+      <c r="J201" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="27.6" customHeight="1" s="19">
       <c r="A202" s="11" t="inlineStr">
@@ -12494,11 +12650,15 @@
       </c>
       <c r="H202" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I202" s="11" t="n"/>
-      <c r="J202" s="12" t="n"/>
+      <c r="J202" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="27.6" customHeight="1" s="19">
       <c r="A203" s="11" t="inlineStr">
@@ -12536,11 +12696,15 @@
       </c>
       <c r="H203" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I203" s="11" t="n"/>
-      <c r="J203" s="12" t="n"/>
+      <c r="J203" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="27.6" customHeight="1" s="19">
       <c r="A204" s="11" t="inlineStr">
@@ -12578,11 +12742,15 @@
       </c>
       <c r="H204" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I204" s="11" t="n"/>
-      <c r="J204" s="12" t="n"/>
+      <c r="J204" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="27.6" customHeight="1" s="19">
       <c r="A205" s="11" t="inlineStr">
@@ -12620,11 +12788,15 @@
       </c>
       <c r="H205" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I205" s="11" t="n"/>
-      <c r="J205" s="12" t="n"/>
+      <c r="J205" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="27.6" customHeight="1" s="19">
       <c r="A206" s="11" t="inlineStr">
@@ -12662,11 +12834,15 @@
       </c>
       <c r="H206" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I206" s="11" t="n"/>
-      <c r="J206" s="12" t="n"/>
+      <c r="J206" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="27.6" customHeight="1" s="19">
       <c r="A207" s="11" t="inlineStr">
@@ -12704,11 +12880,15 @@
       </c>
       <c r="H207" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I207" s="11" t="n"/>
-      <c r="J207" s="12" t="n"/>
+      <c r="J207" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="41.45" customHeight="1" s="19">
       <c r="A208" s="11" t="inlineStr">
@@ -12746,11 +12926,15 @@
       </c>
       <c r="H208" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I208" s="11" t="n"/>
-      <c r="J208" s="12" t="n"/>
+      <c r="J208" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="27.6" customHeight="1" s="19">
       <c r="A209" s="11" t="inlineStr">
@@ -12788,11 +12972,15 @@
       </c>
       <c r="H209" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I209" s="11" t="n"/>
-      <c r="J209" s="12" t="n"/>
+      <c r="J209" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="55.15" customHeight="1" s="19">
       <c r="A210" s="11" t="inlineStr">
@@ -12830,11 +13018,15 @@
       </c>
       <c r="H210" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I210" s="11" t="n"/>
-      <c r="J210" s="12" t="n"/>
+      <c r="J210" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="41.45" customHeight="1" s="19">
       <c r="A211" s="11" t="inlineStr">
@@ -12872,11 +13064,15 @@
       </c>
       <c r="H211" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I211" s="11" t="n"/>
-      <c r="J211" s="12" t="n"/>
+      <c r="J211" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="41.45" customHeight="1" s="19">
       <c r="A212" s="11" t="inlineStr">
@@ -12914,11 +13110,15 @@
       </c>
       <c r="H212" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I212" s="11" t="n"/>
-      <c r="J212" s="12" t="n"/>
+      <c r="J212" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="55.15" customHeight="1" s="19">
       <c r="A213" s="11" t="inlineStr">
@@ -12956,11 +13156,15 @@
       </c>
       <c r="H213" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I213" s="11" t="n"/>
-      <c r="J213" s="12" t="n"/>
+      <c r="J213" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="41.45" customHeight="1" s="19">
       <c r="A214" s="11" t="inlineStr">
@@ -12998,11 +13202,15 @@
       </c>
       <c r="H214" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I214" s="11" t="n"/>
-      <c r="J214" s="12" t="n"/>
+      <c r="J214" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="27.6" customHeight="1" s="19">
       <c r="A215" s="11" t="inlineStr">
@@ -13040,11 +13248,15 @@
       </c>
       <c r="H215" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I215" s="11" t="n"/>
-      <c r="J215" s="12" t="n"/>
+      <c r="J215" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="27.6" customHeight="1" s="19">
       <c r="A216" s="11" t="inlineStr">
@@ -13082,11 +13294,15 @@
       </c>
       <c r="H216" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I216" s="11" t="n"/>
-      <c r="J216" s="12" t="n"/>
+      <c r="J216" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="27.6" customHeight="1" s="19">
       <c r="A217" s="11" t="inlineStr">
@@ -13124,11 +13340,15 @@
       </c>
       <c r="H217" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I217" s="11" t="n"/>
-      <c r="J217" s="12" t="n"/>
+      <c r="J217" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="27.6" customHeight="1" s="19">
       <c r="A218" s="11" t="inlineStr">
@@ -13166,11 +13386,15 @@
       </c>
       <c r="H218" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I218" s="11" t="n"/>
-      <c r="J218" s="12" t="n"/>
+      <c r="J218" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="27.6" customHeight="1" s="19">
       <c r="A219" s="11" t="inlineStr">
@@ -13208,11 +13432,15 @@
       </c>
       <c r="H219" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I219" s="11" t="n"/>
-      <c r="J219" s="12" t="n"/>
+      <c r="J219" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="41.45" customHeight="1" s="19">
       <c r="A220" s="11" t="inlineStr">
@@ -13726,7 +13954,7 @@
       </c>
       <c r="H230" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I230" s="11" t="n">
@@ -13734,7 +13962,7 @@
       </c>
       <c r="J230" s="12" t="inlineStr">
         <is>
-          <t>hoja_firma.dart + BloqueFirmas en la ficha de la OT.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. hoja_firma.dart + BloqueFirmas en la ficha de la OT.</t>
         </is>
       </c>
     </row>
@@ -14212,11 +14440,15 @@
       </c>
       <c r="H241" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I241" s="11" t="n"/>
-      <c r="J241" s="12" t="n"/>
+      <c r="J241" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="41.45" customHeight="1" s="19">
       <c r="A242" s="11" t="inlineStr">
@@ -14884,11 +15116,15 @@
       </c>
       <c r="H257" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I257" s="11" t="n"/>
-      <c r="J257" s="12" t="n"/>
+      <c r="J257" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="27.6" customHeight="1" s="19">
       <c r="A258" s="11" t="inlineStr">
@@ -14926,11 +15162,15 @@
       </c>
       <c r="H258" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I258" s="11" t="n"/>
-      <c r="J258" s="12" t="n"/>
+      <c r="J258" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="27.6" customHeight="1" s="19">
       <c r="A259" s="11" t="inlineStr">
@@ -14968,11 +15208,15 @@
       </c>
       <c r="H259" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I259" s="11" t="n"/>
-      <c r="J259" s="12" t="n"/>
+      <c r="J259" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="27.6" customHeight="1" s="19">
       <c r="A260" s="11" t="inlineStr">
@@ -15010,11 +15254,15 @@
       </c>
       <c r="H260" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I260" s="11" t="n"/>
-      <c r="J260" s="12" t="n"/>
+      <c r="J260" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="27.6" customHeight="1" s="19">
       <c r="A261" s="11" t="inlineStr">
@@ -15052,11 +15300,15 @@
       </c>
       <c r="H261" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I261" s="11" t="n"/>
-      <c r="J261" s="12" t="n"/>
+      <c r="J261" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="27.6" customHeight="1" s="19">
       <c r="A262" s="11" t="inlineStr">
@@ -15094,11 +15346,15 @@
       </c>
       <c r="H262" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I262" s="11" t="n"/>
-      <c r="J262" s="12" t="n"/>
+      <c r="J262" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="55.15" customHeight="1" s="19">
       <c r="A263" s="11" t="inlineStr">
@@ -15136,11 +15392,15 @@
       </c>
       <c r="H263" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I263" s="11" t="n"/>
-      <c r="J263" s="12" t="n"/>
+      <c r="J263" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="41.45" customHeight="1" s="19">
       <c r="A264" s="11" t="inlineStr">
@@ -15178,11 +15438,15 @@
       </c>
       <c r="H264" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I264" s="11" t="n"/>
-      <c r="J264" s="12" t="n"/>
+      <c r="J264" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="41.45" customHeight="1" s="19">
       <c r="A265" s="11" t="inlineStr">
@@ -15220,11 +15484,15 @@
       </c>
       <c r="H265" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I265" s="11" t="n"/>
-      <c r="J265" s="12" t="n"/>
+      <c r="J265" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="41.45" customHeight="1" s="19">
       <c r="A266" s="11" t="inlineStr">
@@ -15262,11 +15530,15 @@
       </c>
       <c r="H266" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I266" s="11" t="n"/>
-      <c r="J266" s="12" t="n"/>
+      <c r="J266" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="41.45" customHeight="1" s="19">
       <c r="A267" s="11" t="inlineStr">
@@ -15304,11 +15576,15 @@
       </c>
       <c r="H267" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I267" s="11" t="n"/>
-      <c r="J267" s="12" t="n"/>
+      <c r="J267" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="41.45" customHeight="1" s="19">
       <c r="A268" s="11" t="inlineStr">
@@ -15346,11 +15622,15 @@
       </c>
       <c r="H268" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I268" s="11" t="n"/>
-      <c r="J268" s="12" t="n"/>
+      <c r="J268" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="41.45" customHeight="1" s="19">
       <c r="A269" s="11" t="inlineStr">
@@ -15388,11 +15668,15 @@
       </c>
       <c r="H269" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I269" s="11" t="n"/>
-      <c r="J269" s="12" t="n"/>
+      <c r="J269" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="41.45" customHeight="1" s="19">
       <c r="A270" s="11" t="inlineStr">
@@ -15430,11 +15714,15 @@
       </c>
       <c r="H270" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I270" s="11" t="n"/>
-      <c r="J270" s="12" t="n"/>
+      <c r="J270" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="27.6" customHeight="1" s="19">
       <c r="A271" s="11" t="inlineStr">
@@ -15472,11 +15760,15 @@
       </c>
       <c r="H271" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I271" s="11" t="n"/>
-      <c r="J271" s="12" t="n"/>
+      <c r="J271" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="27.6" customHeight="1" s="19">
       <c r="A272" s="11" t="inlineStr">
@@ -15514,11 +15806,15 @@
       </c>
       <c r="H272" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I272" s="11" t="n"/>
-      <c r="J272" s="12" t="n"/>
+      <c r="J272" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="41.45" customHeight="1" s="19">
       <c r="A273" s="11" t="inlineStr">
@@ -15556,11 +15852,15 @@
       </c>
       <c r="H273" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I273" s="11" t="n"/>
-      <c r="J273" s="12" t="n"/>
+      <c r="J273" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="27.6" customHeight="1" s="19">
       <c r="A274" s="11" t="inlineStr">
@@ -15598,11 +15898,15 @@
       </c>
       <c r="H274" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I274" s="11" t="n"/>
-      <c r="J274" s="12" t="n"/>
+      <c r="J274" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="27.6" customHeight="1" s="19">
       <c r="A275" s="11" t="inlineStr">
@@ -15640,11 +15944,15 @@
       </c>
       <c r="H275" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I275" s="11" t="n"/>
-      <c r="J275" s="12" t="n"/>
+      <c r="J275" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="27.6" customHeight="1" s="19">
       <c r="A276" s="11" t="inlineStr">
@@ -15682,11 +15990,15 @@
       </c>
       <c r="H276" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I276" s="11" t="n"/>
-      <c r="J276" s="12" t="n"/>
+      <c r="J276" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="41.45" customHeight="1" s="19">
       <c r="A277" s="11" t="inlineStr">
@@ -15724,11 +16036,15 @@
       </c>
       <c r="H277" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I277" s="11" t="n"/>
-      <c r="J277" s="12" t="n"/>
+      <c r="J277" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="27.6" customHeight="1" s="19">
       <c r="A278" s="11" t="inlineStr">
@@ -15766,11 +16082,15 @@
       </c>
       <c r="H278" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I278" s="11" t="n"/>
-      <c r="J278" s="12" t="n"/>
+      <c r="J278" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="55.15" customHeight="1" s="19">
       <c r="A279" s="11" t="inlineStr">
@@ -15808,11 +16128,15 @@
       </c>
       <c r="H279" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I279" s="11" t="n"/>
-      <c r="J279" s="12" t="n"/>
+      <c r="J279" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="41.45" customHeight="1" s="19">
       <c r="A280" s="11" t="inlineStr">
@@ -16606,11 +16930,15 @@
       </c>
       <c r="H298" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I298" s="11" t="n"/>
-      <c r="J298" s="12" t="n"/>
+      <c r="J298" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="41.45" customHeight="1" s="19">
       <c r="A299" s="11" t="inlineStr">
@@ -17320,11 +17648,15 @@
       </c>
       <c r="H315" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I315" s="11" t="n"/>
-      <c r="J315" s="12" t="n"/>
+      <c r="J315" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="41.45" customHeight="1" s="19">
       <c r="A316" s="11" t="inlineStr">

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
@@ -2254,8 +2254,16 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>Dueño único desde el 27-09-2026: hace desarrollo, pruebas, documentación y validación.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="69" customHeight="1" s="19">
       <c r="A19" s="13" t="inlineStr">
@@ -2691,7 +2699,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>A nombre de Bryan (14-09-2026). Firmas desde la app; sin pantalla web propia (T-5244/5245 quedan Por hacer).</t>
+          <t>A nombre de Bryan. Firmas desde la app (API) y, desde el 27-09-2026, también en la web: un solo cuadro de firma en la pestaña Cierre de la orden, sin modal, con historial y condición derivada. BD/302. Evidencia _scratch/ev_hu118_firma_unica.py 11/11.</t>
         </is>
       </c>
     </row>
@@ -2759,8 +2767,16 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O25" s="14" t="n"/>
-      <c r="P25" s="14" t="n"/>
+      <c r="O25" s="14" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="P25" s="14" t="inlineStr">
+        <is>
+          <t>Dueño único desde el 27-09-2026: hace desarrollo, pruebas, documentación y validación.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="69" customHeight="1" s="19">
       <c r="A26" s="11" t="inlineStr">
@@ -2826,8 +2842,16 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="P26" s="12" t="inlineStr">
+        <is>
+          <t>Dueño único desde el 27-09-2026: hace desarrollo, pruebas, documentación y validación.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55.15" customHeight="1" s="19">
       <c r="A27" s="13" t="inlineStr">
@@ -3035,8 +3059,16 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O29" s="14" t="n"/>
-      <c r="P29" s="14" t="n"/>
+      <c r="O29" s="14" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P29" s="14" t="inlineStr">
+        <is>
+          <t>Dueño único desde el 27-09-2026: hace desarrollo, pruebas, documentación y validación.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="69" customHeight="1" s="19">
       <c r="A30" s="11" t="inlineStr">
@@ -3102,8 +3134,16 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
+      <c r="P30" s="12" t="inlineStr">
+        <is>
+          <t>Dueño único desde el 27-09-2026: hace desarrollo, pruebas, documentación y validación.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="19">
       <c r="A31" s="13" t="inlineStr">
@@ -3169,8 +3209,16 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O31" s="14" t="n"/>
-      <c r="P31" s="14" t="n"/>
+      <c r="O31" s="14" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
+      <c r="P31" s="14" t="inlineStr">
+        <is>
+          <t>Dueño único desde el 27-09-2026: hace desarrollo, pruebas, documentación y validación.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="19">
       <c r="A32" s="15" t="n"/>
@@ -9913,7 +9961,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
@@ -9922,7 +9970,11 @@
         </is>
       </c>
       <c r="I143" s="11" t="n"/>
-      <c r="J143" s="12" t="n"/>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="41.45" customHeight="1" s="19">
       <c r="A144" s="11" t="inlineStr">
@@ -9997,7 +10049,7 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
@@ -10006,7 +10058,11 @@
         </is>
       </c>
       <c r="I145" s="11" t="n"/>
-      <c r="J145" s="12" t="n"/>
+      <c r="J145" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="27.6" customHeight="1" s="19">
       <c r="A146" s="11" t="inlineStr">
@@ -10039,7 +10095,7 @@
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H146" s="11" t="inlineStr">
@@ -10048,7 +10104,11 @@
         </is>
       </c>
       <c r="I146" s="11" t="n"/>
-      <c r="J146" s="12" t="n"/>
+      <c r="J146" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="27.6" customHeight="1" s="19">
       <c r="A147" s="11" t="inlineStr">
@@ -10123,7 +10183,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H148" s="11" t="inlineStr">
@@ -10132,7 +10192,11 @@
         </is>
       </c>
       <c r="I148" s="11" t="n"/>
-      <c r="J148" s="12" t="n"/>
+      <c r="J148" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="27.6" customHeight="1" s="19">
       <c r="A149" s="11" t="inlineStr">
@@ -10249,7 +10313,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
@@ -10258,7 +10322,11 @@
         </is>
       </c>
       <c r="I151" s="11" t="n"/>
-      <c r="J151" s="12" t="n"/>
+      <c r="J151" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="27.6" customHeight="1" s="19">
       <c r="A152" s="11" t="inlineStr">
@@ -10291,7 +10359,7 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H152" s="11" t="inlineStr">
@@ -10300,7 +10368,11 @@
         </is>
       </c>
       <c r="I152" s="11" t="n"/>
-      <c r="J152" s="12" t="n"/>
+      <c r="J152" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="27.6" customHeight="1" s="19">
       <c r="A153" s="11" t="inlineStr">
@@ -13862,13 +13934,15 @@
       </c>
       <c r="H228" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I228" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I228" s="11" t="n">
+        <v>1.5</v>
+      </c>
       <c r="J228" s="12" t="inlineStr">
         <is>
-          <t>Sin pantalla web propia en este bloque: las firmas se registran desde la app (hoja_firma) y se ven en la ficha web como validaciones.</t>
+          <t>Sin pantalla web propia en este bloque: las firmas se registran desde la app (hoja_firma) y se ven en la ficha web como validaciones. · 27-09-2026: la firma se registra en la pestaña Cierre de la orden, SIN ficha aparte: un solo cuadro de firma con tipo (aceptación/ejecución/validación), resultado, observación y trazo; «Registrar firma» o «Firmar y cerrar OT». Escribe por API_INS_ORDEN_TRABAJO_VALIDACION (el SP de la app). BD/302.</t>
         </is>
       </c>
     </row>
@@ -13908,13 +13982,15 @@
       </c>
       <c r="H229" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I229" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I229" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J229" s="12" t="inlineStr">
         <is>
-          <t>Idem T-5244.</t>
+          <t>Idem T-5244. · 27-09-2026: el historial de firmas vive en la orden (pestaña Cierre), no en un listado aparte: tipo, resultado, quién, cuándo, observación y la firma; más la condición derivada Validada / Validación rechazada / Sin validar (SEL_ORDEN_TRABAJO_VALIDACION, BD/302).</t>
         </is>
       </c>
     </row>
@@ -14141,7 +14217,7 @@
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H234" s="11" t="inlineStr">
@@ -14150,7 +14226,11 @@
         </is>
       </c>
       <c r="I234" s="11" t="n"/>
-      <c r="J234" s="12" t="n"/>
+      <c r="J234" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="27.6" customHeight="1" s="19">
       <c r="A235" s="11" t="inlineStr">
@@ -14183,7 +14263,7 @@
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H235" s="11" t="inlineStr">
@@ -14192,7 +14272,11 @@
         </is>
       </c>
       <c r="I235" s="11" t="n"/>
-      <c r="J235" s="12" t="n"/>
+      <c r="J235" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="27.6" customHeight="1" s="19">
       <c r="A236" s="11" t="inlineStr">
@@ -14267,7 +14351,7 @@
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H237" s="11" t="inlineStr">
@@ -14276,7 +14360,11 @@
         </is>
       </c>
       <c r="I237" s="11" t="n"/>
-      <c r="J237" s="12" t="n"/>
+      <c r="J237" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="41.45" customHeight="1" s="19">
       <c r="A238" s="11" t="inlineStr">
@@ -14309,7 +14397,7 @@
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H238" s="11" t="inlineStr">
@@ -14318,7 +14406,11 @@
         </is>
       </c>
       <c r="I238" s="11" t="n"/>
-      <c r="J238" s="12" t="n"/>
+      <c r="J238" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="41.45" customHeight="1" s="19">
       <c r="A239" s="11" t="inlineStr">
@@ -14351,7 +14443,7 @@
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H239" s="11" t="inlineStr">
@@ -14360,7 +14452,11 @@
         </is>
       </c>
       <c r="I239" s="11" t="n"/>
-      <c r="J239" s="12" t="n"/>
+      <c r="J239" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="27.6" customHeight="1" s="19">
       <c r="A240" s="11" t="inlineStr">
@@ -14393,7 +14489,7 @@
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H240" s="11" t="inlineStr">
@@ -14402,7 +14498,11 @@
         </is>
       </c>
       <c r="I240" s="11" t="n"/>
-      <c r="J240" s="12" t="n"/>
+      <c r="J240" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="55.15" customHeight="1" s="19">
       <c r="A241" s="11" t="inlineStr">
@@ -14481,7 +14581,7 @@
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H242" s="11" t="inlineStr">
@@ -14490,7 +14590,11 @@
         </is>
       </c>
       <c r="I242" s="11" t="n"/>
-      <c r="J242" s="12" t="n"/>
+      <c r="J242" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="27.6" customHeight="1" s="19">
       <c r="A243" s="11" t="inlineStr">
@@ -14607,7 +14711,7 @@
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H245" s="11" t="inlineStr">
@@ -14616,7 +14720,11 @@
         </is>
       </c>
       <c r="I245" s="11" t="n"/>
-      <c r="J245" s="12" t="n"/>
+      <c r="J245" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="41.45" customHeight="1" s="19">
       <c r="A246" s="11" t="inlineStr">
@@ -14691,7 +14799,7 @@
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H247" s="11" t="inlineStr">
@@ -14700,7 +14808,11 @@
         </is>
       </c>
       <c r="I247" s="11" t="n"/>
-      <c r="J247" s="12" t="n"/>
+      <c r="J247" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="27.6" customHeight="1" s="19">
       <c r="A248" s="11" t="inlineStr">
@@ -14733,7 +14845,7 @@
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H248" s="11" t="inlineStr">
@@ -14742,7 +14854,11 @@
         </is>
       </c>
       <c r="I248" s="11" t="n"/>
-      <c r="J248" s="12" t="n"/>
+      <c r="J248" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="27.6" customHeight="1" s="19">
       <c r="A249" s="11" t="inlineStr">
@@ -14817,7 +14933,7 @@
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H250" s="11" t="inlineStr">
@@ -14826,7 +14942,11 @@
         </is>
       </c>
       <c r="I250" s="11" t="n"/>
-      <c r="J250" s="12" t="n"/>
+      <c r="J250" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="27.6" customHeight="1" s="19">
       <c r="A251" s="11" t="inlineStr">
@@ -14859,7 +14979,7 @@
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H251" s="11" t="inlineStr">
@@ -14868,7 +14988,11 @@
         </is>
       </c>
       <c r="I251" s="11" t="n"/>
-      <c r="J251" s="12" t="n"/>
+      <c r="J251" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="55.15" customHeight="1" s="19">
       <c r="A252" s="11" t="inlineStr">
@@ -14901,7 +15025,7 @@
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H252" s="11" t="inlineStr">
@@ -14910,7 +15034,11 @@
         </is>
       </c>
       <c r="I252" s="11" t="n"/>
-      <c r="J252" s="12" t="n"/>
+      <c r="J252" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="41.45" customHeight="1" s="19">
       <c r="A253" s="11" t="inlineStr">
@@ -14943,7 +15071,7 @@
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H253" s="11" t="inlineStr">
@@ -14952,7 +15080,11 @@
         </is>
       </c>
       <c r="I253" s="11" t="n"/>
-      <c r="J253" s="12" t="n"/>
+      <c r="J253" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="41.45" customHeight="1" s="19">
       <c r="A254" s="11" t="inlineStr">
@@ -14985,7 +15117,7 @@
       </c>
       <c r="G254" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H254" s="11" t="inlineStr">
@@ -14994,7 +15126,11 @@
         </is>
       </c>
       <c r="I254" s="11" t="n"/>
-      <c r="J254" s="12" t="n"/>
+      <c r="J254" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="41.45" customHeight="1" s="19">
       <c r="A255" s="11" t="inlineStr">
@@ -16211,7 +16347,7 @@
       </c>
       <c r="G281" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H281" s="11" t="inlineStr">
@@ -16220,7 +16356,11 @@
         </is>
       </c>
       <c r="I281" s="11" t="n"/>
-      <c r="J281" s="12" t="n"/>
+      <c r="J281" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="41.45" customHeight="1" s="19">
       <c r="A282" s="11" t="inlineStr">
@@ -16253,7 +16393,7 @@
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H282" s="11" t="inlineStr">
@@ -16262,7 +16402,11 @@
         </is>
       </c>
       <c r="I282" s="11" t="n"/>
-      <c r="J282" s="12" t="n"/>
+      <c r="J282" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="41.45" customHeight="1" s="19">
       <c r="A283" s="11" t="inlineStr">
@@ -16337,7 +16481,7 @@
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H284" s="11" t="inlineStr">
@@ -16346,7 +16490,11 @@
         </is>
       </c>
       <c r="I284" s="11" t="n"/>
-      <c r="J284" s="12" t="n"/>
+      <c r="J284" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="27.6" customHeight="1" s="19">
       <c r="A285" s="11" t="inlineStr">
@@ -16379,7 +16527,7 @@
       </c>
       <c r="G285" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H285" s="11" t="inlineStr">
@@ -16388,7 +16536,11 @@
         </is>
       </c>
       <c r="I285" s="11" t="n"/>
-      <c r="J285" s="12" t="n"/>
+      <c r="J285" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="27.6" customHeight="1" s="19">
       <c r="A286" s="11" t="inlineStr">
@@ -16421,7 +16573,7 @@
       </c>
       <c r="G286" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H286" s="11" t="inlineStr">
@@ -16430,7 +16582,11 @@
         </is>
       </c>
       <c r="I286" s="11" t="n"/>
-      <c r="J286" s="12" t="n"/>
+      <c r="J286" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="27.6" customHeight="1" s="19">
       <c r="A287" s="11" t="inlineStr">
@@ -16463,7 +16619,7 @@
       </c>
       <c r="G287" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H287" s="11" t="inlineStr">
@@ -16472,7 +16628,11 @@
         </is>
       </c>
       <c r="I287" s="11" t="n"/>
-      <c r="J287" s="12" t="n"/>
+      <c r="J287" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="27.6" customHeight="1" s="19">
       <c r="A288" s="11" t="inlineStr">
@@ -16547,7 +16707,7 @@
       </c>
       <c r="G289" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H289" s="11" t="inlineStr">
@@ -16556,7 +16716,11 @@
         </is>
       </c>
       <c r="I289" s="11" t="n"/>
-      <c r="J289" s="12" t="n"/>
+      <c r="J289" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="55.15" customHeight="1" s="19">
       <c r="A290" s="11" t="inlineStr">
@@ -16589,7 +16753,7 @@
       </c>
       <c r="G290" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H290" s="11" t="inlineStr">
@@ -16598,7 +16762,11 @@
         </is>
       </c>
       <c r="I290" s="11" t="n"/>
-      <c r="J290" s="12" t="n"/>
+      <c r="J290" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="41.45" customHeight="1" s="19">
       <c r="A291" s="11" t="inlineStr">
@@ -16673,7 +16841,7 @@
       </c>
       <c r="G292" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H292" s="11" t="inlineStr">
@@ -16682,7 +16850,11 @@
         </is>
       </c>
       <c r="I292" s="11" t="n"/>
-      <c r="J292" s="12" t="n"/>
+      <c r="J292" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="41.45" customHeight="1" s="19">
       <c r="A293" s="11" t="inlineStr">
@@ -16715,7 +16887,7 @@
       </c>
       <c r="G293" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H293" s="11" t="inlineStr">
@@ -16724,7 +16896,11 @@
         </is>
       </c>
       <c r="I293" s="11" t="n"/>
-      <c r="J293" s="12" t="n"/>
+      <c r="J293" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="27.6" customHeight="1" s="19">
       <c r="A294" s="11" t="inlineStr">
@@ -16799,7 +16975,7 @@
       </c>
       <c r="G295" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H295" s="11" t="inlineStr">
@@ -16808,7 +16984,11 @@
         </is>
       </c>
       <c r="I295" s="11" t="n"/>
-      <c r="J295" s="12" t="n"/>
+      <c r="J295" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="27.6" customHeight="1" s="19">
       <c r="A296" s="11" t="inlineStr">
@@ -16841,7 +17021,7 @@
       </c>
       <c r="G296" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H296" s="11" t="inlineStr">
@@ -16850,7 +17030,11 @@
         </is>
       </c>
       <c r="I296" s="11" t="n"/>
-      <c r="J296" s="12" t="n"/>
+      <c r="J296" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="27.6" customHeight="1" s="19">
       <c r="A297" s="11" t="inlineStr">
@@ -16971,7 +17155,7 @@
       </c>
       <c r="G299" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H299" s="11" t="inlineStr">
@@ -16980,7 +17164,11 @@
         </is>
       </c>
       <c r="I299" s="11" t="n"/>
-      <c r="J299" s="12" t="n"/>
+      <c r="J299" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="41.45" customHeight="1" s="19">
       <c r="A300" s="11" t="inlineStr">
@@ -17013,7 +17201,7 @@
       </c>
       <c r="G300" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H300" s="11" t="inlineStr">
@@ -17022,7 +17210,11 @@
         </is>
       </c>
       <c r="I300" s="11" t="n"/>
-      <c r="J300" s="12" t="n"/>
+      <c r="J300" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="27.6" customHeight="1" s="19">
       <c r="A301" s="11" t="inlineStr">
@@ -17055,7 +17247,7 @@
       </c>
       <c r="G301" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H301" s="11" t="inlineStr">
@@ -17064,7 +17256,11 @@
         </is>
       </c>
       <c r="I301" s="11" t="n"/>
-      <c r="J301" s="12" t="n"/>
+      <c r="J301" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="27.6" customHeight="1" s="19">
       <c r="A302" s="11" t="inlineStr">
@@ -17097,7 +17293,7 @@
       </c>
       <c r="G302" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H302" s="11" t="inlineStr">
@@ -17106,7 +17302,11 @@
         </is>
       </c>
       <c r="I302" s="11" t="n"/>
-      <c r="J302" s="12" t="n"/>
+      <c r="J302" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="27.6" customHeight="1" s="19">
       <c r="A303" s="11" t="inlineStr">
@@ -17181,7 +17381,7 @@
       </c>
       <c r="G304" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H304" s="11" t="inlineStr">
@@ -17190,7 +17390,11 @@
         </is>
       </c>
       <c r="I304" s="11" t="n"/>
-      <c r="J304" s="12" t="n"/>
+      <c r="J304" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="41.45" customHeight="1" s="19">
       <c r="A305" s="11" t="inlineStr">
@@ -17223,7 +17427,7 @@
       </c>
       <c r="G305" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H305" s="11" t="inlineStr">
@@ -17232,7 +17436,11 @@
         </is>
       </c>
       <c r="I305" s="11" t="n"/>
-      <c r="J305" s="12" t="n"/>
+      <c r="J305" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="41.45" customHeight="1" s="19">
       <c r="A306" s="11" t="inlineStr">
@@ -17307,7 +17515,7 @@
       </c>
       <c r="G307" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H307" s="11" t="inlineStr">
@@ -17316,7 +17524,11 @@
         </is>
       </c>
       <c r="I307" s="11" t="n"/>
-      <c r="J307" s="12" t="n"/>
+      <c r="J307" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="41.45" customHeight="1" s="19">
       <c r="A308" s="11" t="inlineStr">
@@ -17391,7 +17603,7 @@
       </c>
       <c r="G309" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H309" s="11" t="inlineStr">
@@ -17400,7 +17612,11 @@
         </is>
       </c>
       <c r="I309" s="11" t="n"/>
-      <c r="J309" s="12" t="n"/>
+      <c r="J309" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="27.6" customHeight="1" s="19">
       <c r="A310" s="11" t="inlineStr">
@@ -17475,7 +17691,7 @@
       </c>
       <c r="G311" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H311" s="11" t="inlineStr">
@@ -17484,7 +17700,11 @@
         </is>
       </c>
       <c r="I311" s="11" t="n"/>
-      <c r="J311" s="12" t="n"/>
+      <c r="J311" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="27.6" customHeight="1" s="19">
       <c r="A312" s="11" t="inlineStr">
@@ -17517,7 +17737,7 @@
       </c>
       <c r="G312" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H312" s="11" t="inlineStr">
@@ -17526,7 +17746,11 @@
         </is>
       </c>
       <c r="I312" s="11" t="n"/>
-      <c r="J312" s="12" t="n"/>
+      <c r="J312" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="27.6" customHeight="1" s="19">
       <c r="A313" s="11" t="inlineStr">
@@ -17601,7 +17825,7 @@
       </c>
       <c r="G314" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H314" s="11" t="inlineStr">
@@ -17610,7 +17834,11 @@
         </is>
       </c>
       <c r="I314" s="11" t="n"/>
-      <c r="J314" s="12" t="n"/>
+      <c r="J314" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="41.45" customHeight="1" s="19">
       <c r="A315" s="11" t="inlineStr">
@@ -17731,7 +17959,7 @@
       </c>
       <c r="G317" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H317" s="11" t="inlineStr">
@@ -17740,7 +17968,11 @@
         </is>
       </c>
       <c r="I317" s="11" t="n"/>
-      <c r="J317" s="12" t="n"/>
+      <c r="J317" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="41.45" customHeight="1" s="19">
       <c r="A318" s="11" t="inlineStr">
@@ -17773,7 +18005,7 @@
       </c>
       <c r="G318" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H318" s="11" t="inlineStr">
@@ -17782,7 +18014,11 @@
         </is>
       </c>
       <c r="I318" s="11" t="n"/>
-      <c r="J318" s="12" t="n"/>
+      <c r="J318" s="12" t="inlineStr">
+        <is>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="27.6" customHeight="1" s="19"/>
     <row r="320" ht="27.6" customHeight="1" s="19"/>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
@@ -514,51 +514,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1257120</colOff>
-      <row>3</row>
-      <rowOff>37440</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="211320" y="190440"/>
-          <a:ext cx="1257120" cy="418680"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1169,7 +1124,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16892,13 +16846,15 @@
       </c>
       <c r="H293" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I293" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I293" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J293" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez. | BD/431: bre_uuid + indice unico filtrado; API_INS_BITACORA_RECTIFICACION idempotente por uuid (reenvio devuelve la que ya estaba). DTO suma uuid y el controller lo pasa. Aplicado en dev, API compila.</t>
         </is>
       </c>
     </row>
@@ -16938,11 +16894,17 @@
       </c>
       <c r="H294" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I294" s="11" t="n"/>
-      <c r="J294" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I294" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J294" s="12" t="inlineStr">
+        <is>
+          <t>GET /bitacora/{id}/rectificaciones (lista, reusa modo 4) y GET /bitacora/rectificaciones/{bre} (detalle con SP dedicado BD/432, filtrado por cliente, 404 si no existe). API compila.</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="41.45" customHeight="1" s="19">
       <c r="A295" s="11" t="inlineStr">
@@ -16980,13 +16942,15 @@
       </c>
       <c r="H295" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I295" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I295" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J295" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez. | Validacion del cuerpo en el controller antes del SP: texto y motivo obligatorios (ExigirTexto) y motivo &lt;=500 (largo de bre_motivo); 400 claro sin viaje a la base. El SP queda de backstop. API compila.</t>
         </is>
       </c>
     </row>
@@ -17026,13 +16990,15 @@
       </c>
       <c r="H296" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I296" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I296" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J296" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez. | Formulario de rectificar integrado en la ficha del activo (boton por nota, texto corregido prellenado + motivo obligatorio). Postback a lnkRectificar -&gt; ActivoCentroController.RectificarBitacora (mismo SP que la app, idempotente por uuid). Intranet compila.</t>
         </is>
       </c>
     </row>
@@ -17072,11 +17038,17 @@
       </c>
       <c r="H297" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I297" s="11" t="n"/>
-      <c r="J297" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I297" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J297" s="12" t="inlineStr">
+        <is>
+          <t>Integrado en la ficha del activo (no pantalla suelta): cada entrada rectificada muestra el original tachado y la cadena de rectificaciones con motivo/autor/fecha, la ultima como vigente (chip Rectificada). SP SEL_ACTIVO_BITACORA_RECTIFICACION (BD/433). Intranet compila.</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="27.6" customHeight="1" s="19">
       <c r="A298" s="11" t="inlineStr">
@@ -17160,13 +17132,15 @@
       </c>
       <c r="H299" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I299" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I299" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J299" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez. | RectificarBitacora exige REGISTRAR BITACORA (Token.Puede) en el servidor, no escondiendo el boton; autor-only y filtro por cliente en sesion los impone ademas el SP. Lectura acotada por cliente de sesion. Intranet compila.</t>
         </is>
       </c>
     </row>
@@ -17206,13 +17180,15 @@
       </c>
       <c r="H300" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I300" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I300" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J300" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio. | Un caso por criterio ejecutado contra la BD en transaccion con ROLLBACK (no persiste): CA-2 original se conserva + idempotencia uuid (YA_ESTABA=1), CA-3 motivo obligatorio rechazado, solo-el-autor rechazado, CA-1 comentario append-only. Resultados en Criterios (Verificado=Si, filas 82-84) e Informe de Pruebas S5 (seccion HU-131).</t>
         </is>
       </c>
     </row>
@@ -20602,7 +20578,7 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -20634,7 +20610,7 @@
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -20665,7 +20641,7 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
@@ -17228,13 +17228,15 @@
       </c>
       <c r="H301" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I301" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I301" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J301" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio. | Swagger: los endpoints de rectificacion documentados con XML (summary + response, idempotencia por uuid en el 201); Swagger ya incluye bin/API.xml. MD de estado: decisiones no deducibles del codigo anotadas en SIGMA_ESTADO_DESARROLLO_API.md (nested vs recurso suelto, uuid, SP de detalle, validacion) y en el doc principal (integracion web en la ficha del activo).</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
@@ -1212,6 +1212,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -2251,7 +2253,7 @@
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -3056,7 +3058,7 @@
       </c>
       <c r="N29" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O29" s="14" t="inlineStr">
@@ -3330,6 +3332,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -9966,13 +9970,15 @@
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I143" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I143" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>Orden_Trabajo_Servicio (BD/263) revisada: FK a OT, proveedor, tipo y moneda; índices IX_OTS_ORDEN_TRABAJO e IX_OTS_PROVEEDOR. Nace ots_archivo_informe (FK Archivo) para el informe del proveedor (BD/430).</t>
         </is>
       </c>
     </row>
@@ -10012,11 +10018,17 @@
       </c>
       <c r="H144" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I144" s="11" t="n"/>
-      <c r="J144" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I144" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J144" s="12" t="inlineStr">
+        <is>
+          <t>INS_ORDEN_TRABAJO_SERVICIO (BD/430): valida OT del cliente y no cerrada, proveedor del cliente, tipo, descripción, monto &gt; 0 y moneda; devuelve el id.</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="27.6" customHeight="1" s="19">
       <c r="A145" s="11" t="inlineStr">
@@ -10054,13 +10066,15 @@
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I145" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+          <t>SEL_ORDEN_TRABAJO_SERVICIO ampliado (ids, informe), SEL_OT_SERVICIO_TOTAL (costo de terceros separado por moneda) y SEL_OT_SERVICIO_SIN_INFORME (BD/430).</t>
         </is>
       </c>
     </row>
@@ -10100,13 +10114,15 @@
       </c>
       <c r="H146" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I146" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J146" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>UPD_ORDEN_TRABAJO_SERVICIO y DEL_ (baja lógica) solo con la OT no cerrada; UPD_ORDEN_TRABAJO_SERVICIO_INFORME liga el archivo (BD/430).</t>
         </is>
       </c>
     </row>
@@ -10146,11 +10162,17 @@
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I147" s="11" t="n"/>
-      <c r="J147" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J147" s="12" t="inlineStr">
+        <is>
+          <t>OT-3 de Hamburgo: un servicio en CLP (350.000) y otro en UF (4,5), documentos FAC-PRUEBA-117-1/2 (_scratch/prueba_hu117.sql).</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="41.45" customHeight="1" s="19">
       <c r="A148" s="11" t="inlineStr">
@@ -10188,13 +10210,15 @@
       </c>
       <c r="H148" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I148" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I148" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J148" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+          <t>Rediseño: no es una página aparte. «Registrar servicio» abre el cajón de la ficha de la OT (Órdenes › OT › Pasos y consumo) con proveedor, tipo, descripción, monto, moneda, documento, fecha e informe en un solo paso (sigma-mant-ordenes.js, WsOrdenes.GuardarServicio).</t>
         </is>
       </c>
     </row>
@@ -10234,11 +10258,17 @@
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I149" s="11" t="n"/>
-      <c r="J149" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I149" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J149" s="12" t="inlineStr">
+        <is>
+          <t>Rediseño: el listado vive en la sección «Servicios contratados» de la OT, con el estado del informe de cada línea (adjunto / falta), editar, quitar y el costo de terceros por moneda.</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="27.6" customHeight="1" s="19">
       <c r="A150" s="11" t="inlineStr">
@@ -10276,11 +10306,17 @@
       </c>
       <c r="H150" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I150" s="11" t="n"/>
-      <c r="J150" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I150" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J150" s="12" t="inlineStr">
+        <is>
+          <t>WsOrdenes exige «CREAR ORDEN TRABAJO» para registrar, corregir, quitar o adjuntar; los SP filtran por el cliente en sesión. El cierre (Cerrar) rechaza en el servidor una OT con servicios sin informe.</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="27.6" customHeight="1" s="19">
       <c r="A151" s="11" t="inlineStr">
@@ -10318,13 +10354,15 @@
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I151" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I151" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J151" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>CA1, CA2 y CA3 ejecutados en desa (_scratch/prueba_hu117.sql): registro, total por moneda (CLP y UF separados), bloqueo del cierre sin informe, y rechazos de monto 0, OT cerrada y otro cliente.</t>
         </is>
       </c>
     </row>
@@ -10364,13 +10402,15 @@
       </c>
       <c r="H152" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I152" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J152" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>Sin endpoint REST: los métodos son de la Intranet (WsOrdenes.asmx: ServicioCatalogos, GuardarServicio, QuitarServicio, InformeServicio). Decisiones anotadas en MD/SIGMA_ESTADO_DESARROLLO.md (bitácora 10-10-2026).</t>
         </is>
       </c>
     </row>
@@ -16310,11 +16350,17 @@
       </c>
       <c r="H280" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I280" s="11" t="n"/>
-      <c r="J280" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I280" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J280" s="12" t="inlineStr">
+        <is>
+          <t>Orden_Trabajo revisada: lo que se imprime ya existe en SEL_ORDEN_TRABAJO (cierre, motivo, quién cerró). Faltaba el encabezado del cliente.</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="41.45" customHeight="1" s="19">
       <c r="A281" s="11" t="inlineStr">
@@ -16352,13 +16398,15 @@
       </c>
       <c r="H281" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I281" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I281" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J281" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+          <t>SEL_ORDEN_TRABAJO_IMPRIMIR (BD/431): encabezado del cliente (razón social, RUT, logo) acotado al cliente en sesión, todo por parámetros.</t>
         </is>
       </c>
     </row>
@@ -16398,13 +16446,15 @@
       </c>
       <c r="H282" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I282" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I282" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J282" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>Índices por orden en Orden_Trabajo_Paso y Orden_Trabajo_Validacion si faltaban (BD/431); servicios, repuestos y mano de obra ya los tenían.</t>
         </is>
       </c>
     </row>
@@ -16444,11 +16494,17 @@
       </c>
       <c r="H283" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I283" s="11" t="n"/>
-      <c r="J283" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I283" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J283" s="12" t="inlineStr">
+        <is>
+          <t>Se usan OT-3 (abierta, con pasos y servicios) y OT-4 (cerrada) de Hamburgo.</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="27.6" customHeight="1" s="19">
       <c r="A284" s="11" t="inlineStr">
@@ -16486,13 +16542,15 @@
       </c>
       <c r="H284" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I284" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I284" s="11" t="n">
+        <v>1.5</v>
+      </c>
       <c r="J284" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+          <t>OrdenTrabajoImprimir.aspx: hoja A4 con encabezado del cliente, datos, pasos, repuestos, mano de obra, servicios con total por moneda, cierre y firmas (registradas o en blanco). Botón «Imprimir» en la cabecera de la OT: abre la pestaña y lanza la impresión sola.</t>
         </is>
       </c>
     </row>
@@ -16532,13 +16590,15 @@
       </c>
       <c r="H285" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I285" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I285" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J285" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+          <t>La página exige sesión y «VER ORDENES TRABAJO» en el servidor; la OT se busca con el cliente en sesión (otro cliente no obtiene nada, probado).</t>
         </is>
       </c>
     </row>
@@ -16578,13 +16638,15 @@
       </c>
       <c r="H286" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I286" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I286" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J286" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>CA1 y CA2: el SP de impresión responde para el cliente y rechaza otro cliente; la hoja de una OT cerrada incluye resultado, motivo de cierre y firmas. Compila con aspnet_compiler.</t>
         </is>
       </c>
     </row>
@@ -16624,13 +16686,15 @@
       </c>
       <c r="H287" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I287" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I287" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J287" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>Sin endpoint REST: es una página de la Intranet. Decisiones anotadas en el MD de estado (bitácora 10-10-2026).</t>
         </is>
       </c>
     </row>
@@ -18121,6 +18185,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -19462,7 +19528,7 @@
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19560,7 @@
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19591,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20605,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -20570,7 +20636,7 @@
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
@@ -16624,11 +16624,17 @@
       </c>
       <c r="H288" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I288" s="11" t="n"/>
-      <c r="J288" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I288" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J288" s="12" t="inlineStr">
+        <is>
+          <t>Modelo Bitacora_Rectificacion existe (BD/23): columnas, FK a Bitacora y Usuario, indices PK + IX_BRE_BITACORA + UX_BRE_UUID (unico por uuid, BD/431). Esta tabla no tiene 'codigo', ese punto de la plantilla no aplica.</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="41.45" customHeight="1" s="19">
       <c r="A289" s="11" t="inlineStr">
@@ -16666,13 +16672,15 @@
       </c>
       <c r="H289" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I289" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I289" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J289" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio. | SP de alta transaccional existe: API_INS_BITACORA_RECTIFICACION (devuelve bre_id; idempotente por uuid tras BD/431). Cumple el rol del INS_BITACORA_RECTIFICACION de la plantilla.</t>
         </is>
       </c>
     </row>
@@ -16712,13 +16720,15 @@
       </c>
       <c r="H290" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I290" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I290" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J290" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez. | SP SEL existe: API_SEL_BITACORA_RECTIFICACION (detalle por id, BD/432) + listado por API_SEL_BITACORA modo 4 + SEL_ACTIVO_BITACORA_RECTIFICACION (ficha web, BD/433).</t>
         </is>
       </c>
     </row>
@@ -16758,11 +16768,15 @@
       </c>
       <c r="H291" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Descartada</t>
         </is>
       </c>
       <c r="I291" s="11" t="n"/>
-      <c r="J291" s="12" t="n"/>
+      <c r="J291" s="12" t="inlineStr">
+        <is>
+          <t>Descartada por diseno: la bitacora es append-only. Rectificar es agregar otra fila, no editar; un UPD_BITACORA_RECTIFICACION contradice los criterios «la original se conserva» y «no se edita ni elimina» de la HU.</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="41.45" customHeight="1" s="19">
       <c r="A292" s="11" t="inlineStr">
@@ -16800,13 +16814,15 @@
       </c>
       <c r="H292" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I292" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I292" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J292" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio. | Datos de prueba: BD/434 deja 2 rectificaciones de demo en una entrada con activo (ACT-10 Dosificador de Manteca, bit_id 9), idempotente por uuid fijo.</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
@@ -17292,13 +17292,15 @@
       </c>
       <c r="H302" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I302" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I302" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J302" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez. | Usuario_Accesibilidad ya existia (BD/07, una fila por usuario). Para CA-4 se agregaron uac_volumen y uac_silenciar_alertas (BD/435). Sin 'codigo' (no aplica).</t>
         </is>
       </c>
     </row>
@@ -17338,11 +17340,17 @@
       </c>
       <c r="H303" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I303" s="11" t="n"/>
-      <c r="J303" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I303" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J303" s="12" t="inlineStr">
+        <is>
+          <t>SEL_USUARIO_ACCESIBILIDAD (BD/436): un SP para la ficha (por id) y las 'mias' (por usuario), con filtros opcionales.</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="55.15" customHeight="1" s="19">
       <c r="A304" s="11" t="inlineStr">
@@ -17380,13 +17388,15 @@
       </c>
       <c r="H304" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I304" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I304" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J304" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio. | INS_USUARIO_ACCESIBILIDAD (BD/437): alta transaccional, una fila por usuario, fecha con FNC_PAIS_HORA, id por OUTPUT.</t>
         </is>
       </c>
     </row>
@@ -17426,13 +17436,15 @@
       </c>
       <c r="H305" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I305" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I305" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J305" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez. | UPD_USUARIO_ACCESIBILIDAD (BD/438): ISNULL(@X,columna) para no borrar lo no enviado.</t>
         </is>
       </c>
     </row>
@@ -17472,11 +17484,17 @@
       </c>
       <c r="H306" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I306" s="11" t="n"/>
-      <c r="J306" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I306" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J306" s="12" t="inlineStr">
+        <is>
+          <t>DEL_USUARIO_ACCESIBILIDAD (BD/439): baja logica (uac_habilitado=0); sin dependientes.</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="27.6" customHeight="1" s="19">
       <c r="A307" s="11" t="inlineStr">
@@ -17514,13 +17532,15 @@
       </c>
       <c r="H307" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I307" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I307" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J307" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio. | Datos de prueba (BD/440): fila demo con texto grande, alto contraste y volumen 0.5.</t>
         </is>
       </c>
     </row>
@@ -17560,11 +17580,17 @@
       </c>
       <c r="H308" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I308" s="11" t="n"/>
-      <c r="J308" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I308" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J308" s="12" t="inlineStr">
+        <is>
+          <t>GET /usuario-accesibilidades: las opciones de quien llama (por usuario del token); DTO sin columnas internas.</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="27.6" customHeight="1" s="19">
       <c r="A309" s="11" t="inlineStr">
@@ -17602,13 +17628,15 @@
       </c>
       <c r="H309" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I309" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I309" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J309" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez. | GET /{id}: detalle propio; 404 si el id no es tuyo.</t>
         </is>
       </c>
     </row>
@@ -17648,11 +17676,17 @@
       </c>
       <c r="H310" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I310" s="11" t="n"/>
-      <c r="J310" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I310" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J310" s="12" t="inlineStr">
+        <is>
+          <t>POST: alta del usuario del token; valida el cuerpo; el error del SP sale como 400.</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="27.6" customHeight="1" s="19">
       <c r="A311" s="11" t="inlineStr">
@@ -17690,13 +17724,15 @@
       </c>
       <c r="H311" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I311" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I311" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J311" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez. | PUT edita lo propio (ISNULL); DELETE baja logica; EsMia verifica la propiedad.</t>
         </is>
       </c>
     </row>
@@ -17736,13 +17772,15 @@
       </c>
       <c r="H312" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I312" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I312" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J312" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez. | Pantalla Accesibilidad de autoservicio con el diseno estandar; carga las opciones del usuario. No grilla admin: es por usuario.</t>
         </is>
       </c>
     </row>
@@ -17782,11 +17820,17 @@
       </c>
       <c r="H313" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I313" s="11" t="n"/>
-      <c r="J313" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I313" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J313" s="12" t="inlineStr">
+        <is>
+          <t>Guardar (INS/UPD) + aplicar en todas las pantallas: el master pone clases en el body y sigma-accesibilidad-global.css las implementa; movimiento reducido por prefers-reduced-motion.</t>
+        </is>
+      </c>
     </row>
     <row r="314" ht="55.15" customHeight="1" s="19">
       <c r="A314" s="11" t="inlineStr">
@@ -17824,13 +17868,15 @@
       </c>
       <c r="H314" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I314" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I314" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J314" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez. | Permiso CONFIGURAR ACCESIBILIDAD a todos los perfiles + menu bajo Utilidades (BD/441).</t>
         </is>
       </c>
     </row>
@@ -17916,11 +17962,17 @@
       </c>
       <c r="H316" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I316" s="11" t="n"/>
-      <c r="J316" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I316" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J316" s="12" t="inlineStr">
+        <is>
+          <t>Escrituras autorizadas en el servidor (web Token.Puede, API ExigirPermiso), no escondiendo el boton; se toca solo lo propio.</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="41.45" customHeight="1" s="19">
       <c r="A317" s="11" t="inlineStr">
@@ -17958,13 +18010,15 @@
       </c>
       <c r="H317" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I317" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I317" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J317" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio. | Un caso por criterio; persistencia (guardar/releer/conservar/una fila por usuario) verificada en transaccion con ROLLBACK (PASS); Informe de Pruebas S5 y Criterios.</t>
         </is>
       </c>
     </row>
@@ -18004,13 +18058,15 @@
       </c>
       <c r="H318" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I318" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I318" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J318" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio.</t>
+          <t>Reparto por historia completa (27-09-2026): antes Catalina Pescio. | Swagger (XML docs, bin/API.xml) + decisiones en los MD de estado (por usuario, no CRUD admin; columnas de sonido; movimiento reducido por el SO).</t>
         </is>
       </c>
     </row>
@@ -20690,7 +20746,7 @@
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -20721,7 +20777,7 @@
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20809,7 @@
       </c>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -20785,7 +20841,7 @@
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
@@ -1212,8 +1212,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -2766,7 +2764,7 @@
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
@@ -2776,7 +2774,7 @@
       </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>Dueño único desde el 27-09-2026: hace desarrollo, pruebas, documentación y validación.</t>
+          <t>Dueño único desde el 27-09-2026. Galería en la ficha de la OT y del activo (web) y GET /api/archivo-vinculos para la app (BD/429–436). Tareas de Catalina terminadas; el consumo desde la app (T-5257) pasó al Sprint 6. Pendiente validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2839,7 @@
       </c>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="O26" s="12" t="inlineStr">
@@ -2851,7 +2849,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>Dueño único desde el 27-09-2026: hace desarrollo, pruebas, documentación y validación.</t>
+          <t>Dueño único desde el 27-09-2026. Hecho: modelo revisado y las referencias ya se muestran separadas en la galería del activo (chip «Referencias») y de la OT («Cómo debe quedar»). Falta adjuntar la referencia desde la actividad del plan y el ítem de pauta.</t>
         </is>
       </c>
     </row>
@@ -3332,8 +3330,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -14262,13 +14258,15 @@
       </c>
       <c r="H234" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I234" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I234" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J234" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Archivo_Vinculo revisada: no hace falta tabla nueva. La galería del equipo sale por Orden_Trabajo.otr_activo (CK_AVI_UN_PADRE impide que una foto de OT traiga avi_activo); avi_es_referencia está sobrecargado (trampa en el MD). BD/429.</t>
         </is>
       </c>
     </row>
@@ -14308,13 +14306,15 @@
       </c>
       <c r="H235" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I235" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I235" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J235" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+          <t>BD/430 SEL_ARCHIVO_VINCULO: un SP para las dos galerías (@ORDEN_TRABAJO por paso y momento, @ACTIVO por fecha), filtros @MOMENTO, @SOLO_IMAGENES, @INCLUIR_REFERENCIAS, paginación @PAGINA/@TAMANO con TOTAL; todo por parámetros, sin firma, deshabilitados ni otro cliente. BD/436 suma la RUTA para la API.</t>
         </is>
       </c>
     </row>
@@ -14354,11 +14354,17 @@
       </c>
       <c r="H236" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I236" s="11" t="n"/>
-      <c r="J236" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I236" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J236" s="12" t="inlineStr">
+        <is>
+          <t>BD/429: índices filtrados IX_AVI_OT_PASO, IX_AVI_PAA e IX_AVI_CPI.</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="55.15" customHeight="1" s="19">
       <c r="A237" s="11" t="inlineStr">
@@ -14396,13 +14402,15 @@
       </c>
       <c r="H237" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I237" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I237" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J237" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>BD/_SEMILLA_GALERIA_EVIDENCIAS.sql: 12 archivos PRUEBA_HU142_* en OT 1, 5 (ACT-10) y 2, con momentos, PDF, firma y uno deshabilitado, reutilizando blobs existentes (sin los videos rotos 19 y 20).</t>
         </is>
       </c>
     </row>
@@ -14442,13 +14450,15 @@
       </c>
       <c r="H238" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I238" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I238" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J238" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+          <t>GET /api/archivo-vinculos (ArchivoVinculosController): ?orden_trabajo= o ?activo=, filtros momento, solo_imagenes, incluir_referencias y paginado en el servidor (Paginado.DeServidor, 2 pruebas xUnit). Exige VER ORDENES TRABAJO o VER ACTIVOS; la imagen se pide por /archivo/ver, que valida el cliente.</t>
         </is>
       </c>
     </row>
@@ -14488,13 +14498,15 @@
       </c>
       <c r="H239" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I239" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I239" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J239" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Caché corta de 30 s en GET /archivo-vinculos (cambia el contenido, no los permisos): segunda llamada 5 ms contra 851 ms.</t>
         </is>
       </c>
     </row>
@@ -14534,13 +14546,15 @@
       </c>
       <c r="H240" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I240" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I240" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J240" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+          <t>Rediseño: no es ArchivoVinculo.aspx suelta. La galería vive en la ficha de la OT (pestaña Pasos, por paso y momento, filtro por momento, visor MantKit.Visor con flechas y Descargar) y en la ficha del activo (BD/435 SEL_ACTIVO_ARCHIVO_TODO suma las fotos de los pasos: ACT-10 pasa de 3 a 9).</t>
         </is>
       </c>
     </row>
@@ -14626,13 +14640,15 @@
       </c>
       <c r="H242" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I242" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I242" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J242" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+          <t>WsOrdenes.Ficha/Galeria exigen VER ORDENES TRABAJO; la API exige VER ORDENES TRABAJO o VER ACTIVOS; el SP filtra por cliente y VerArchivo vuelve a exigirlo (ruta de otro cliente = 401).</t>
         </is>
       </c>
     </row>
@@ -14672,11 +14688,17 @@
       </c>
       <c r="H243" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I243" s="11" t="n"/>
-      <c r="J243" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I243" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J243" s="12" t="inlineStr">
+        <is>
+          <t>CA1 y CA2 ejecutados en desa con la semilla: OT-1 = 6 por paso y momento, ampliar y descargar en el visor; ACT-10 = 9 por fecha, sin la falla de OT 2. Además filtros, página 2, otro cliente = 0 y parámetros malos = 400 por HTTP. Verificado en el navegador (Hamburgo) y a 375 px.</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="27.6" customHeight="1" s="19">
       <c r="A244" s="11" t="inlineStr">
@@ -14714,11 +14736,17 @@
       </c>
       <c r="H244" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I244" s="11" t="n"/>
-      <c r="J244" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I244" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J244" s="12" t="inlineStr">
+        <is>
+          <t>Endpoint documentado con comentarios XML en ArchivoVinculosController (Swagger). Decisiones en MD/SIGMA_ESTADO_DESARROLLO.md, bitácora 10 y 11-10-2026 (pasos 1 a 4) y trampa de avi_es_referencia.</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="27.6" customHeight="1" s="19">
       <c r="A245" s="11" t="inlineStr">
@@ -14756,13 +14784,15 @@
       </c>
       <c r="H245" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I245" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I245" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J245" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+          <t>Revisado junto con T-5250: una imagen de referencia se reconoce por su destino (avi_plan_mantenimiento_actividad o avi_checklist_plantilla_item), no por avi_es_referencia ni por la categoría 10. Índices IX_AVI_PAA e IX_AVI_CPI (BD/429).</t>
         </is>
       </c>
     </row>
@@ -18185,8 +18215,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -20290,7 +20318,7 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -20321,7 +20349,7 @@
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -20416,7 +20444,7 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S5.xlsx
@@ -2793,7 +2793,7 @@
       </c>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O26" s="12" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>Dueño único desde el 27-09-2026. Hecho: modelo revisado y las referencias ya se muestran separadas en la galería del activo (chip «Referencias») y de la OT («Cómo debe quedar»). Falta adjuntar la referencia desde la actividad del plan y el ítem de pauta.</t>
+          <t>Dueño único desde el 27-09-2026. Imagen de referencia en la actividad del plan (Centro de Planificación) y en el ítem de pauta (Biblioteca); la ve quien ejecuta en la OT y en la inspección de Operación (BD/454). Pendiente validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -14786,11 +14786,17 @@
       </c>
       <c r="H246" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I246" s="11" t="n"/>
-      <c r="J246" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I246" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J246" s="12" t="inlineStr">
+        <is>
+          <t>BD/454 SEL_ARCHIVO_REFERENCIA: por id, por actividades o ítems (ids separados por coma) o por pauta (versión que muestra el cajón: borrador si existe, si no la publicada). Todo por parámetros, filtrado por cliente.</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="27.6" customHeight="1" s="19">
       <c r="A247" s="11" t="inlineStr">
@@ -14828,13 +14834,15 @@
       </c>
       <c r="H247" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I247" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I247" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J247" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>BD/454 INS_ARCHIVO_REFERENCIA: en transacción; un solo destino (actividad o ítem), solo imágenes del cliente, tope 6 por destino. Sin código propio: la referencia es un archivo pegado a su destino (no aplica «código único»). El ítem llega por código de la pauta, porque el id cambia con cada versión.</t>
         </is>
       </c>
     </row>
@@ -14874,13 +14882,15 @@
       </c>
       <c r="H248" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I248" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I248" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J248" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+          <t>BD/454 UPD_ARCHIVO_REFERENCIA: solo el texto «qué debe verse»; el resto del vínculo no se toca.</t>
         </is>
       </c>
     </row>
@@ -14920,11 +14930,17 @@
       </c>
       <c r="H249" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I249" s="11" t="n"/>
-      <c r="J249" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I249" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J249" s="12" t="inlineStr">
+        <is>
+          <t>BD/454 DEL_ARCHIVO_REFERENCIA: baja lógica (el archivo puede seguir en otra versión del plan o la pauta). Además, los SP que clonan planes y pautas copian las referencias y los que borran borradores las quitan antes (FK_AVI_PAA / FK_AVI_CPI).</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="27.6" customHeight="1" s="19">
       <c r="A250" s="11" t="inlineStr">
@@ -14962,13 +14978,15 @@
       </c>
       <c r="H250" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I250" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I250" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J250" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>BD/Semillas/_SEMILLA_REFERENCIAS_HU143.sql: referencia en la primera actividad del plan 1 (publicada y borrador) y en el primer ítem de PAU-001, reutilizando fotos de la semilla de HU-142.</t>
         </is>
       </c>
     </row>
@@ -15008,13 +15026,15 @@
       </c>
       <c r="H251" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I251" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I251" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J251" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>Rediseño (regla «solo cajón»): no hay listado aparte. En el Centro de Planificación, bloque «Imagen de referencia» en el cajón de la actividad; en Biblioteca › Pautas, un botón por ítem abre su panel de referencias, con la etiqueta «n referencias» en la fila.</t>
         </is>
       </c>
     </row>
@@ -15054,13 +15074,15 @@
       </c>
       <c r="H252" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I252" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I252" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J252" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Emilio Fuentes.</t>
+          <t>Rediseño: sin RadWindow. Subir (JPG/PNG/WEBP, 8 MB), texto «qué debe verse» y quitar, en el mismo cajón; se guarda al momento, sin abrir borrador ni publicar versión. Al ejecutar: la OT la muestra en «Cómo debe quedar» y la inspección de Operación junto a la pregunta, con el visor.</t>
         </is>
       </c>
     </row>
@@ -15100,13 +15122,15 @@
       </c>
       <c r="H253" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I253" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I253" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J253" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>No hay pantallas nuevas: viven en Planificación, Biblioteca y Operación, que ya están en Menus con su permiso. Sin filas nuevas en Menus.</t>
         </is>
       </c>
     </row>
@@ -15146,13 +15170,15 @@
       </c>
       <c r="H254" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I254" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I254" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J254" s="12" t="inlineStr">
         <is>
-          <t>Reparto por historia completa (27-09-2026): antes Bryan Chávez.</t>
+          <t>WsCentroPlanificacion exige CREAR EDITAR PLANES MANTENIMIENTO y que el plan sea del cliente; WsRecursos exige CREAR EDITAR PAUTAS; los SP vuelven a exigir el cliente de la actividad, del ítem y del archivo.</t>
         </is>
       </c>
     </row>
@@ -15192,11 +15218,17 @@
       </c>
       <c r="H255" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I255" s="11" t="n"/>
-      <c r="J255" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I255" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J255" s="12" t="inlineStr">
+        <is>
+          <t>CA1 y CA2 ejecutados: SP en transacción deshecha (rechazos, tope, título, descartar borrador, versión nueva y borrador de pauta heredan la referencia) y navegador con Hamburgo: subir, titular y quitar en la actividad y en el ítem; la OT-1 la muestra como referencia y la inspección PAU-001 junto a la pregunta, con visor; sin errores de consola ni scroll a 375 px.</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="41.45" customHeight="1" s="19">
       <c r="A256" s="11" t="inlineStr">
@@ -15234,11 +15266,17 @@
       </c>
       <c r="H256" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I256" s="11" t="n"/>
-      <c r="J256" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I256" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J256" s="12" t="inlineStr">
+        <is>
+          <t>Sin endpoint REST: son métodos de la Intranet (WsCentroPlanificacion: AgregarReferencia, TituloReferencia, QuitarReferencia; WsRecursos: AgregarReferenciaItem, TituloReferenciaItem, QuitarReferenciaItem). Decisiones en MD/SIGMA_ESTADO_DESARROLLO.md (bitácora 12-10-2026) y trampa del versionado en Boveda/Trampas conocidas.</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="27.6" customHeight="1" s="19">
       <c r="A257" s="11" t="inlineStr">
@@ -20431,7 +20469,7 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -20462,7 +20500,7 @@
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
